--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP66"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12101,6 +12101,3452 @@
       <c r="BO66" t="inlineStr"/>
       <c r="BP66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>49</v>
+      </c>
+      <c r="L67" t="n">
+        <v>51</v>
+      </c>
+      <c r="M67" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14</v>
+      </c>
+      <c r="O67" t="n">
+        <v>5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>9</v>
+      </c>
+      <c r="R67" t="n">
+        <v>8</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>167</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>2837500</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>1614500</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>23.90476190476191</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>179.1428571428571</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>63.76190476190476</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>1497619.047619048</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>69.42857142857143</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>1414750</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>120</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>52</v>
+      </c>
+      <c r="L68" t="n">
+        <v>48</v>
+      </c>
+      <c r="M68" t="n">
+        <v>17</v>
+      </c>
+      <c r="N68" t="n">
+        <v>15</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2</v>
+      </c>
+      <c r="P68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>12</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>167</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>179.9090909090909</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>2684090.909090909</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>2979545.454545455</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>27.29166666666667</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>66</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>1034166.666666667</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>68.29166666666667</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>26.26086956521739</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>179.6086956521739</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>1714347.826086957</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>69.34782608695652</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>126</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>135</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20738</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>40</v>
+      </c>
+      <c r="L69" t="n">
+        <v>60</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3</v>
+      </c>
+      <c r="N69" t="n">
+        <v>16</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>18</v>
+      </c>
+      <c r="R69" t="n">
+        <v>12</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>167</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>28.18181818181818</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>179.2727272727273</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>178.2727272727273</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>4084090.909090909</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>28.35294117647059</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>184.2352941176471</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>1570294.117647059</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>66.94117647058823</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>27.54545454545455</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>180.8181818181818</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>68.59090909090909</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>1727272.727272727</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>850000</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>123</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>46</v>
+      </c>
+      <c r="L70" t="n">
+        <v>54</v>
+      </c>
+      <c r="M70" t="n">
+        <v>8</v>
+      </c>
+      <c r="N70" t="n">
+        <v>19</v>
+      </c>
+      <c r="O70" t="n">
+        <v>8</v>
+      </c>
+      <c r="P70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>11</v>
+      </c>
+      <c r="R70" t="n">
+        <v>9</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>167</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>181.5454545454545</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>3052272.727272727</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>25.52173913043478</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>182.0869565217391</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>63.52173913043478</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>1379565.217391304</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>68.52173913043478</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>24.76470588235294</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>179.7647058823529</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>63.52941176470588</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>988235.2941176471</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>69.70588235294117</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>174</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>206</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>229</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>254</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>19925000</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>53</v>
+      </c>
+      <c r="L71" t="n">
+        <v>47</v>
+      </c>
+      <c r="M71" t="n">
+        <v>18</v>
+      </c>
+      <c r="N71" t="n">
+        <v>9</v>
+      </c>
+      <c r="O71" t="n">
+        <v>5</v>
+      </c>
+      <c r="P71" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>12</v>
+      </c>
+      <c r="R71" t="n">
+        <v>11</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>167</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1914090.909090909</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1617000</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>25.21739130434782</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>180.1739130434783</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>63.17391304347826</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>824130.4347826086</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>68.30434782608695</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>26.91304347826087</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>179.5652173913043</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>68.60869565217391</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>2040217.391304348</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>71.56521739130434</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>184</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>725000</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  mo </t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>55</v>
+      </c>
+      <c r="L72" t="n">
+        <v>45</v>
+      </c>
+      <c r="M72" t="n">
+        <v>28</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12</v>
+      </c>
+      <c r="O72" t="n">
+        <v>11</v>
+      </c>
+      <c r="P72" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>16</v>
+      </c>
+      <c r="R72" t="n">
+        <v>11</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>167</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>69</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>23.18181818181818</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>63.09090909090909</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1259545.454545455</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>583500</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>2055750</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>208</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>198</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>59</v>
+      </c>
+      <c r="L73" t="n">
+        <v>41</v>
+      </c>
+      <c r="M73" t="n">
+        <v>16</v>
+      </c>
+      <c r="N73" t="n">
+        <v>14</v>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>15</v>
+      </c>
+      <c r="R73" t="n">
+        <v>10</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>167</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AE73" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>2287500</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>1577500</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>22.71428571428572</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>62.71428571428572</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>1660714.285714286</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>69.78571428571429</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>179.2916666666667</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>62.54166666666666</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>968750</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>69.58333333333333</v>
+      </c>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>118</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>45462.86458333334</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24795</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>54</v>
+      </c>
+      <c r="L74" t="n">
+        <v>46</v>
+      </c>
+      <c r="M74" t="n">
+        <v>15</v>
+      </c>
+      <c r="N74" t="n">
+        <v>10</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>9</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>167</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>3593181.818181818</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>2544545.454545455</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>61.58333333333334</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>1104375</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>22.06666666666667</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>889000</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>138</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>141</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>178.8333333333333</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>424</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>16175000</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+      <c r="L75" t="n">
+        <v>48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>8</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>167</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>22.36363636363636</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>178.1818181818182</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>65.36363636363636</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1397727.272727273</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>22.45454545454545</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>181</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>64.72727272727273</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>1592727.272727273</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>179.7272727272727</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>67.86363636363636</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>1842045.454545455</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>72.04545454545455</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>22.58823529411765</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>178.9411764705882</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>62.94117647058823</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>1093529.411764706</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>71.64705882352941</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>185</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>202</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>170</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F76" t="n">
+        <v>28301</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>39</v>
+      </c>
+      <c r="L76" t="n">
+        <v>61</v>
+      </c>
+      <c r="M76" t="n">
+        <v>10</v>
+      </c>
+      <c r="N76" t="n">
+        <v>23</v>
+      </c>
+      <c r="O76" t="n">
+        <v>6</v>
+      </c>
+      <c r="P76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>167</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>66.90909090909091</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1868181.818181818</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2998333.333333333</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>181.9411764705882</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>63.64705882352941</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>69.17647058823529</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>23.27272727272727</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>2370454.545454545</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>106</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>615000</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F77" t="n">
+        <v>15899</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>56</v>
+      </c>
+      <c r="L77" t="n">
+        <v>44</v>
+      </c>
+      <c r="M77" t="n">
+        <v>19</v>
+      </c>
+      <c r="N77" t="n">
+        <v>10</v>
+      </c>
+      <c r="O77" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>11</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>167</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>184.9090909090909</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1272727.272727273</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>5464000</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>23.93333333333333</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>62.06666666666667</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>977333.3333333334</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>69.06666666666666</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>62.78571428571428</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>635714.2857142857</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>68.35714285714286</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>312</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>352</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>414</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F78" t="n">
+        <v>19939</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>34</v>
+      </c>
+      <c r="L78" t="n">
+        <v>66</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" t="n">
+        <v>7</v>
+      </c>
+      <c r="P78" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>167</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>69.81818181818181</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>3447727.272727273</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>902083.3333333334</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>69.16666666666667</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>25.65217391304348</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>182.0434782608696</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>64.39130434782609</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>976086.9565217391</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>69.34782608695652</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>587</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>78425000</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>636</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>37</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>63</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F79" t="n">
+        <v>23361</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>51</v>
+      </c>
+      <c r="L79" t="n">
+        <v>49</v>
+      </c>
+      <c r="M79" t="n">
+        <v>16</v>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="n">
+        <v>5</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>15</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>167</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>3237500</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>27.54545454545455</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>68.09090909090909</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>3147727.272727273</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>22.15789473684211</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>177.1578947368421</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>62.57894736842105</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>1565526.315789474</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>70.21052631578948</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>27.04347826086957</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>183.4782608695652</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>63.56521739130435</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>897391.3043478261</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>65.95652173913044</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>395</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>5965000</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>407</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>392</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>C05gWToT</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>45462.95833333334</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wiseman t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laney college football stadium
+  oakland  ca </t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3247</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>41</v>
+      </c>
+      <c r="L80" t="n">
+        <v>59</v>
+      </c>
+      <c r="M80" t="n">
+        <v>15</v>
+      </c>
+      <c r="N80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>13</v>
+      </c>
+      <c r="R80" t="n">
+        <v>12</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>A7iCSGM</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>U31kqHh</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>167</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr"/>
+      <c r="BN80" t="inlineStr"/>
+      <c r="BO80" t="inlineStr"/>
+      <c r="BP80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Y96kX9WM</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calderon c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3009</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>46</v>
+      </c>
+      <c r="L81" t="n">
+        <v>54</v>
+      </c>
+      <c r="M81" t="n">
+        <v>13</v>
+      </c>
+      <c r="N81" t="n">
+        <v>7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>6</v>
+      </c>
+      <c r="P81" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>15</v>
+      </c>
+      <c r="R81" t="n">
+        <v>22</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>vucevHG</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>zVUAOJS</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>167</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>GYBpYkHG</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>45462.875</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>61</v>
+      </c>
+      <c r="L82" t="n">
+        <v>39</v>
+      </c>
+      <c r="M82" t="n">
+        <v>20</v>
+      </c>
+      <c r="N82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="n">
+        <v>10</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>13</v>
+      </c>
+      <c r="R82" t="n">
+        <v>15</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>v7f8zS6</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>6X9nrWK</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>167</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>UuhLRmfp</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thompson m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5084</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>45</v>
+      </c>
+      <c r="L83" t="n">
+        <v>55</v>
+      </c>
+      <c r="M83" t="n">
+        <v>9</v>
+      </c>
+      <c r="N83" t="n">
+        <v>10</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>13</v>
+      </c>
+      <c r="R83" t="n">
+        <v>17</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>j7eIjow</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>IorPEfz</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>167</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+      <c r="AX83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr"/>
+      <c r="BA83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="inlineStr"/>
+      <c r="BN83" t="inlineStr"/>
+      <c r="BO83" t="inlineStr"/>
+      <c r="BP83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>xrDtZV1A</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>45461.97916666666</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cashman field
+  las vegas  nv </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>61</v>
+      </c>
+      <c r="L84" t="n">
+        <v>39</v>
+      </c>
+      <c r="M84" t="n">
+        <v>17</v>
+      </c>
+      <c r="N84" t="n">
+        <v>10</v>
+      </c>
+      <c r="O84" t="n">
+        <v>5</v>
+      </c>
+      <c r="P84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>13</v>
+      </c>
+      <c r="R84" t="n">
+        <v>17</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>zDeq7Oq</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>6V8Ndys</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>167</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+      <c r="AX84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr"/>
+      <c r="BA84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr"/>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="inlineStr"/>
+      <c r="BM84" t="inlineStr"/>
+      <c r="BN84" t="inlineStr"/>
+      <c r="BO84" t="inlineStr"/>
+      <c r="BP84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP66"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12101,6 +12101,3424 @@
       <c r="BO66" t="inlineStr"/>
       <c r="BP66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>49</v>
+      </c>
+      <c r="L67" t="n">
+        <v>51</v>
+      </c>
+      <c r="M67" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14</v>
+      </c>
+      <c r="O67" t="n">
+        <v>5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>9</v>
+      </c>
+      <c r="R67" t="n">
+        <v>8</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>167</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>2837500</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>65.11111111111111</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>1616111.111111111</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>23.90476190476191</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>179.1428571428571</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>63.76190476190476</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>1497619.047619048</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>69.42857142857143</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>1414750</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>120</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>52</v>
+      </c>
+      <c r="L68" t="n">
+        <v>48</v>
+      </c>
+      <c r="M68" t="n">
+        <v>17</v>
+      </c>
+      <c r="N68" t="n">
+        <v>15</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2</v>
+      </c>
+      <c r="P68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>12</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>167</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>179.9090909090909</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>2684090.909090909</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>2979545.454545455</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>27.29166666666667</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>66</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>1034166.666666667</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>68.29166666666667</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>26.26086956521739</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>179.6086956521739</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>1714347.826086957</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>69.34782608695652</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>800000</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>68</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20738</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>40</v>
+      </c>
+      <c r="L69" t="n">
+        <v>60</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3</v>
+      </c>
+      <c r="N69" t="n">
+        <v>16</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>18</v>
+      </c>
+      <c r="R69" t="n">
+        <v>12</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>167</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>28.18181818181818</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>179.2727272727273</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>178.2727272727273</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>4084090.909090909</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>28.35294117647059</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>184.2352941176471</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>1570294.117647059</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>66.94117647058823</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>27.54545454545455</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>180.8181818181818</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>68.59090909090909</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>1727272.727272727</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>188</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>850000</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>123</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>46</v>
+      </c>
+      <c r="L70" t="n">
+        <v>54</v>
+      </c>
+      <c r="M70" t="n">
+        <v>8</v>
+      </c>
+      <c r="N70" t="n">
+        <v>19</v>
+      </c>
+      <c r="O70" t="n">
+        <v>8</v>
+      </c>
+      <c r="P70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>11</v>
+      </c>
+      <c r="R70" t="n">
+        <v>9</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>167</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>181.5454545454545</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>3052272.727272727</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>25.52173913043478</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>182.0869565217391</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>63.52173913043478</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>1379565.217391304</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>68.52173913043478</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>25.29411764705882</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>178.3529411764706</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>64.94117647058823</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>1058823.529411765</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>70.05882352941177</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>174</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>206</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>15450000</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>229</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>254</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>19925000</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>53</v>
+      </c>
+      <c r="L71" t="n">
+        <v>47</v>
+      </c>
+      <c r="M71" t="n">
+        <v>18</v>
+      </c>
+      <c r="N71" t="n">
+        <v>9</v>
+      </c>
+      <c r="O71" t="n">
+        <v>5</v>
+      </c>
+      <c r="P71" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>12</v>
+      </c>
+      <c r="R71" t="n">
+        <v>11</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>167</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1914090.909090909</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1617000</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>25.21739130434782</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>180.1739130434783</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>63.17391304347826</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>824130.4347826086</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>68.30434782608695</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>2166250</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>184</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>66</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>725000</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  mo </t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>55</v>
+      </c>
+      <c r="L72" t="n">
+        <v>45</v>
+      </c>
+      <c r="M72" t="n">
+        <v>28</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12</v>
+      </c>
+      <c r="O72" t="n">
+        <v>11</v>
+      </c>
+      <c r="P72" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>16</v>
+      </c>
+      <c r="R72" t="n">
+        <v>11</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>167</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>69</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>23.18181818181818</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>63.09090909090909</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1259545.454545455</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>583500</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>2055750</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>208</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>198</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>59</v>
+      </c>
+      <c r="L73" t="n">
+        <v>41</v>
+      </c>
+      <c r="M73" t="n">
+        <v>16</v>
+      </c>
+      <c r="N73" t="n">
+        <v>14</v>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>15</v>
+      </c>
+      <c r="R73" t="n">
+        <v>10</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>167</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AE73" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>2287500</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>1577500</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>22.71428571428572</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>62.71428571428572</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>1660714.285714286</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>69.78571428571429</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>179.2916666666667</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>62.54166666666666</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>968750</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>69.58333333333333</v>
+      </c>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>118</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>45462.86458333334</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24795</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>54</v>
+      </c>
+      <c r="L74" t="n">
+        <v>46</v>
+      </c>
+      <c r="M74" t="n">
+        <v>15</v>
+      </c>
+      <c r="N74" t="n">
+        <v>10</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>9</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>167</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>3593181.818181818</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>2544545.454545455</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>61.58333333333334</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>1104375</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>22.06666666666667</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>889000</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
+      <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr"/>
+      <c r="BJ74" t="inlineStr"/>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="inlineStr"/>
+      <c r="BM74" t="inlineStr"/>
+      <c r="BN74" t="inlineStr"/>
+      <c r="BO74" t="inlineStr"/>
+      <c r="BP74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+      <c r="L75" t="n">
+        <v>48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>8</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>167</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>22.36363636363636</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>178.1818181818182</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>65.36363636363636</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1397727.272727273</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>22.45454545454545</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>181</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>64.72727272727273</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>1592727.272727273</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>179.7272727272727</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>67.86363636363636</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>1842045.454545455</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>72.04545454545455</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>22.58823529411765</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>178.9411764705882</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>62.94117647058823</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>1093529.411764706</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>71.64705882352941</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>185</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>202</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>170</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F76" t="n">
+        <v>28301</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>39</v>
+      </c>
+      <c r="L76" t="n">
+        <v>61</v>
+      </c>
+      <c r="M76" t="n">
+        <v>10</v>
+      </c>
+      <c r="N76" t="n">
+        <v>23</v>
+      </c>
+      <c r="O76" t="n">
+        <v>6</v>
+      </c>
+      <c r="P76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>167</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>66.90909090909091</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1868181.818181818</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2998333.333333333</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>181.9411764705882</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>63.64705882352941</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>69.17647058823529</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>23.27272727272727</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>2370454.545454545</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>106</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>615000</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F77" t="n">
+        <v>15899</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>56</v>
+      </c>
+      <c r="L77" t="n">
+        <v>44</v>
+      </c>
+      <c r="M77" t="n">
+        <v>19</v>
+      </c>
+      <c r="N77" t="n">
+        <v>10</v>
+      </c>
+      <c r="O77" t="n">
+        <v>5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>11</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>167</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>184.9090909090909</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1272727.272727273</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>179.6363636363636</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>66.18181818181819</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>5033181.818181818</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>23.93333333333333</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>62.06666666666667</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>977333.3333333334</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>69.06666666666666</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>25.73333333333333</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>179.8666666666667</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>62.93333333333333</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>641666.6666666666</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>68.13333333333334</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>312</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>352</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>414</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F78" t="n">
+        <v>19939</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>34</v>
+      </c>
+      <c r="L78" t="n">
+        <v>66</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" t="n">
+        <v>7</v>
+      </c>
+      <c r="P78" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>167</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>69.81818181818181</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>3447727.272727273</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>902083.3333333334</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>69.16666666666667</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>25.65217391304348</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>182.0434782608696</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>64.39130434782609</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>976086.9565217391</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>69.34782608695652</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>587</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>78425000</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>636</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>37</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>63</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F79" t="n">
+        <v>23361</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>51</v>
+      </c>
+      <c r="L79" t="n">
+        <v>49</v>
+      </c>
+      <c r="M79" t="n">
+        <v>16</v>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="n">
+        <v>5</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>15</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>167</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>3237500</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>27.54545454545455</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>68.09090909090909</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>3147727.272727273</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>22.15789473684211</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>177.1578947368421</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>62.57894736842105</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>1565526.315789474</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>70.21052631578948</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>27.04347826086957</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>183.4782608695652</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>63.56521739130435</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>897391.3043478261</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>65.95652173913044</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>395</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>5965000</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>407</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>392</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>C05gWToT</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>45462.95833333334</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wiseman t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laney college football stadium
+  oakland  ca </t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3247</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>41</v>
+      </c>
+      <c r="L80" t="n">
+        <v>59</v>
+      </c>
+      <c r="M80" t="n">
+        <v>15</v>
+      </c>
+      <c r="N80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>13</v>
+      </c>
+      <c r="R80" t="n">
+        <v>12</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>A7iCSGM</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>U31kqHh</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>167</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr"/>
+      <c r="BN80" t="inlineStr"/>
+      <c r="BO80" t="inlineStr"/>
+      <c r="BP80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Y96kX9WM</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>45462.89583333334</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">calderon c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3009</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>46</v>
+      </c>
+      <c r="L81" t="n">
+        <v>54</v>
+      </c>
+      <c r="M81" t="n">
+        <v>13</v>
+      </c>
+      <c r="N81" t="n">
+        <v>7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>6</v>
+      </c>
+      <c r="P81" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>15</v>
+      </c>
+      <c r="R81" t="n">
+        <v>22</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>vucevHG</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>zVUAOJS</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>167</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>GYBpYkHG</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>45462.875</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>61</v>
+      </c>
+      <c r="L82" t="n">
+        <v>39</v>
+      </c>
+      <c r="M82" t="n">
+        <v>20</v>
+      </c>
+      <c r="N82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="n">
+        <v>10</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>13</v>
+      </c>
+      <c r="R82" t="n">
+        <v>15</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>v7f8zS6</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>6X9nrWK</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>167</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>UuhLRmfp</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>45462.85416666666</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thompson m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5084</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>45</v>
+      </c>
+      <c r="L83" t="n">
+        <v>55</v>
+      </c>
+      <c r="M83" t="n">
+        <v>9</v>
+      </c>
+      <c r="N83" t="n">
+        <v>10</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>13</v>
+      </c>
+      <c r="R83" t="n">
+        <v>17</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>j7eIjow</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>IorPEfz</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>167</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+      <c r="AX83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr"/>
+      <c r="BA83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="inlineStr"/>
+      <c r="BN83" t="inlineStr"/>
+      <c r="BO83" t="inlineStr"/>
+      <c r="BP83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>xrDtZV1A</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>45461.97916666666</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cashman field
+  las vegas  nv </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>61</v>
+      </c>
+      <c r="L84" t="n">
+        <v>39</v>
+      </c>
+      <c r="M84" t="n">
+        <v>17</v>
+      </c>
+      <c r="N84" t="n">
+        <v>10</v>
+      </c>
+      <c r="O84" t="n">
+        <v>5</v>
+      </c>
+      <c r="P84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>13</v>
+      </c>
+      <c r="R84" t="n">
+        <v>17</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>zDeq7Oq</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>6V8Ndys</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>167</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+      <c r="AX84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr"/>
+      <c r="BA84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr"/>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="inlineStr"/>
+      <c r="BM84" t="inlineStr"/>
+      <c r="BN84" t="inlineStr"/>
+      <c r="BO84" t="inlineStr"/>
+      <c r="BP84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP85"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15733,6 +15733,3208 @@
       <c r="BO85" t="inlineStr"/>
       <c r="BP85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F86" t="n">
+        <v>22146</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>59</v>
+      </c>
+      <c r="L86" t="n">
+        <v>41</v>
+      </c>
+      <c r="M86" t="n">
+        <v>27</v>
+      </c>
+      <c r="N86" t="n">
+        <v>15</v>
+      </c>
+      <c r="O86" t="n">
+        <v>8</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>6</v>
+      </c>
+      <c r="R86" t="n">
+        <v>4</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>167</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="inlineStr"/>
+      <c r="AR86" t="inlineStr"/>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr"/>
+      <c r="AX86" t="inlineStr"/>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr"/>
+      <c r="BA86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr"/>
+      <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="inlineStr"/>
+      <c r="BM86" t="inlineStr"/>
+      <c r="BN86" t="inlineStr"/>
+      <c r="BO86" t="inlineStr"/>
+      <c r="BP86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F87" t="n">
+        <v>22471</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>58</v>
+      </c>
+      <c r="L87" t="n">
+        <v>42</v>
+      </c>
+      <c r="M87" t="n">
+        <v>16</v>
+      </c>
+      <c r="N87" t="n">
+        <v>7</v>
+      </c>
+      <c r="O87" t="n">
+        <v>8</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>11</v>
+      </c>
+      <c r="R87" t="n">
+        <v>12</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>167</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AU87" t="inlineStr"/>
+      <c r="AV87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr"/>
+      <c r="AX87" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr"/>
+      <c r="BA87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr"/>
+      <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
+      <c r="BI87" t="inlineStr"/>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="inlineStr"/>
+      <c r="BM87" t="inlineStr"/>
+      <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F88" t="n">
+        <v>30093</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>58</v>
+      </c>
+      <c r="L88" t="n">
+        <v>42</v>
+      </c>
+      <c r="M88" t="n">
+        <v>26</v>
+      </c>
+      <c r="N88" t="n">
+        <v>8</v>
+      </c>
+      <c r="O88" t="n">
+        <v>10</v>
+      </c>
+      <c r="P88" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>17</v>
+      </c>
+      <c r="R88" t="n">
+        <v>13</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>167</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr"/>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr"/>
+      <c r="BA88" t="inlineStr"/>
+      <c r="BB88" t="inlineStr"/>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F89" t="n">
+        <v>15583</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>52</v>
+      </c>
+      <c r="L89" t="n">
+        <v>48</v>
+      </c>
+      <c r="M89" t="n">
+        <v>15</v>
+      </c>
+      <c r="N89" t="n">
+        <v>9</v>
+      </c>
+      <c r="O89" t="n">
+        <v>9</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>7</v>
+      </c>
+      <c r="R89" t="n">
+        <v>5</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
+        <v>167</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
+      <c r="AP89" t="inlineStr"/>
+      <c r="AQ89" t="inlineStr"/>
+      <c r="AR89" t="inlineStr"/>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AU89" t="inlineStr"/>
+      <c r="AV89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr"/>
+      <c r="AX89" t="inlineStr"/>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr"/>
+      <c r="BA89" t="inlineStr"/>
+      <c r="BB89" t="inlineStr"/>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
+      <c r="BM89" t="inlineStr"/>
+      <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F90" t="n">
+        <v>21570</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>58</v>
+      </c>
+      <c r="L90" t="n">
+        <v>42</v>
+      </c>
+      <c r="M90" t="n">
+        <v>13</v>
+      </c>
+      <c r="N90" t="n">
+        <v>8</v>
+      </c>
+      <c r="O90" t="n">
+        <v>4</v>
+      </c>
+      <c r="P90" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>13</v>
+      </c>
+      <c r="R90" t="n">
+        <v>10</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>167</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="inlineStr"/>
+      <c r="AR90" t="inlineStr"/>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AU90" t="inlineStr"/>
+      <c r="AV90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr"/>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
+      <c r="BM90" t="inlineStr"/>
+      <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F91" t="n">
+        <v>19746</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>49</v>
+      </c>
+      <c r="L91" t="n">
+        <v>51</v>
+      </c>
+      <c r="M91" t="n">
+        <v>12</v>
+      </c>
+      <c r="N91" t="n">
+        <v>9</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>18</v>
+      </c>
+      <c r="R91" t="n">
+        <v>15</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>167</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
+      <c r="AP91" t="inlineStr"/>
+      <c r="AQ91" t="inlineStr"/>
+      <c r="AR91" t="inlineStr"/>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AU91" t="inlineStr"/>
+      <c r="AV91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr"/>
+      <c r="AX91" t="inlineStr"/>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr"/>
+      <c r="BA91" t="inlineStr"/>
+      <c r="BB91" t="inlineStr"/>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
+      <c r="BM91" t="inlineStr"/>
+      <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F92" t="n">
+        <v>29663</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>45</v>
+      </c>
+      <c r="L92" t="n">
+        <v>55</v>
+      </c>
+      <c r="M92" t="n">
+        <v>7</v>
+      </c>
+      <c r="N92" t="n">
+        <v>14</v>
+      </c>
+      <c r="O92" t="n">
+        <v>3</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>8</v>
+      </c>
+      <c r="R92" t="n">
+        <v>10</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>167</v>
+      </c>
+      <c r="V92" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="inlineStr"/>
+      <c r="AP92" t="inlineStr"/>
+      <c r="AQ92" t="inlineStr"/>
+      <c r="AR92" t="inlineStr"/>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AU92" t="inlineStr"/>
+      <c r="AV92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr"/>
+      <c r="BA92" t="inlineStr"/>
+      <c r="BB92" t="inlineStr"/>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
+      <c r="BM92" t="inlineStr"/>
+      <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>49</v>
+      </c>
+      <c r="L93" t="n">
+        <v>51</v>
+      </c>
+      <c r="M93" t="n">
+        <v>14</v>
+      </c>
+      <c r="N93" t="n">
+        <v>14</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>11</v>
+      </c>
+      <c r="R93" t="n">
+        <v>13</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>167</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+      <c r="AQ93" t="inlineStr"/>
+      <c r="AR93" t="inlineStr"/>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AU93" t="inlineStr"/>
+      <c r="AV93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr"/>
+      <c r="AX93" t="inlineStr"/>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr"/>
+      <c r="BA93" t="inlineStr"/>
+      <c r="BB93" t="inlineStr"/>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
+      <c r="BM93" t="inlineStr"/>
+      <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F94" t="n">
+        <v>20818</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>66</v>
+      </c>
+      <c r="L94" t="n">
+        <v>34</v>
+      </c>
+      <c r="M94" t="n">
+        <v>13</v>
+      </c>
+      <c r="N94" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" t="n">
+        <v>8</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>16</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>167</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr"/>
+      <c r="AP94" t="inlineStr"/>
+      <c r="AQ94" t="inlineStr"/>
+      <c r="AR94" t="inlineStr"/>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AU94" t="inlineStr"/>
+      <c r="AV94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr"/>
+      <c r="AX94" t="inlineStr"/>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr"/>
+      <c r="BA94" t="inlineStr"/>
+      <c r="BB94" t="inlineStr"/>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
+      <c r="BM94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>17993</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>47</v>
+      </c>
+      <c r="L95" t="n">
+        <v>53</v>
+      </c>
+      <c r="M95" t="n">
+        <v>8</v>
+      </c>
+      <c r="N95" t="n">
+        <v>14</v>
+      </c>
+      <c r="O95" t="n">
+        <v>3</v>
+      </c>
+      <c r="P95" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>19</v>
+      </c>
+      <c r="R95" t="n">
+        <v>11</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
+        <v>167</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr"/>
+      <c r="AP95" t="inlineStr"/>
+      <c r="AQ95" t="inlineStr"/>
+      <c r="AR95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AU95" t="inlineStr"/>
+      <c r="AV95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr"/>
+      <c r="AX95" t="inlineStr"/>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr"/>
+      <c r="BA95" t="inlineStr"/>
+      <c r="BB95" t="inlineStr"/>
+      <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr"/>
+      <c r="BM95" t="inlineStr"/>
+      <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F96" t="n">
+        <v>25513</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>56</v>
+      </c>
+      <c r="L96" t="n">
+        <v>44</v>
+      </c>
+      <c r="M96" t="n">
+        <v>19</v>
+      </c>
+      <c r="N96" t="n">
+        <v>9</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>19</v>
+      </c>
+      <c r="R96" t="n">
+        <v>9</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>167</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr"/>
+      <c r="AP96" t="inlineStr"/>
+      <c r="AQ96" t="inlineStr"/>
+      <c r="AR96" t="inlineStr"/>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AU96" t="inlineStr"/>
+      <c r="AV96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr"/>
+      <c r="AX96" t="inlineStr"/>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr"/>
+      <c r="BA96" t="inlineStr"/>
+      <c r="BB96" t="inlineStr"/>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr"/>
+      <c r="BM96" t="inlineStr"/>
+      <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>43</v>
+      </c>
+      <c r="L97" t="n">
+        <v>57</v>
+      </c>
+      <c r="M97" t="n">
+        <v>15</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>7</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>9</v>
+      </c>
+      <c r="R97" t="n">
+        <v>11</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>167</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
+      <c r="AQ97" t="inlineStr"/>
+      <c r="AR97" t="inlineStr"/>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AU97" t="inlineStr"/>
+      <c r="AV97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr"/>
+      <c r="AX97" t="inlineStr"/>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr"/>
+      <c r="BA97" t="inlineStr"/>
+      <c r="BB97" t="inlineStr"/>
+      <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
+      <c r="BI97" t="inlineStr"/>
+      <c r="BJ97" t="inlineStr"/>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="inlineStr"/>
+      <c r="BM97" t="inlineStr"/>
+      <c r="BN97" t="inlineStr"/>
+      <c r="BO97" t="inlineStr"/>
+      <c r="BP97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F98" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>46</v>
+      </c>
+      <c r="L98" t="n">
+        <v>54</v>
+      </c>
+      <c r="M98" t="n">
+        <v>7</v>
+      </c>
+      <c r="N98" t="n">
+        <v>16</v>
+      </c>
+      <c r="O98" t="n">
+        <v>5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>11</v>
+      </c>
+      <c r="R98" t="n">
+        <v>12</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
+        <v>167</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AU98" t="inlineStr"/>
+      <c r="AV98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr"/>
+      <c r="AX98" t="inlineStr"/>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr"/>
+      <c r="BA98" t="inlineStr"/>
+      <c r="BB98" t="inlineStr"/>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="inlineStr"/>
+      <c r="BM98" t="inlineStr"/>
+      <c r="BN98" t="inlineStr"/>
+      <c r="BO98" t="inlineStr"/>
+      <c r="BP98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F99" t="n">
+        <v>18762</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>56</v>
+      </c>
+      <c r="L99" t="n">
+        <v>44</v>
+      </c>
+      <c r="M99" t="n">
+        <v>16</v>
+      </c>
+      <c r="N99" t="n">
+        <v>18</v>
+      </c>
+      <c r="O99" t="n">
+        <v>8</v>
+      </c>
+      <c r="P99" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>9</v>
+      </c>
+      <c r="R99" t="n">
+        <v>10</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>167</v>
+      </c>
+      <c r="V99" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+      <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="inlineStr"/>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr"/>
+      <c r="AV99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr"/>
+      <c r="AX99" t="inlineStr"/>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr"/>
+      <c r="BA99" t="inlineStr"/>
+      <c r="BB99" t="inlineStr"/>
+      <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="inlineStr"/>
+      <c r="BM99" t="inlineStr"/>
+      <c r="BN99" t="inlineStr"/>
+      <c r="BO99" t="inlineStr"/>
+      <c r="BP99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>W4YFmVG3</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wiseman t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cashman field
+  las vegas  nv </t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1657</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>62</v>
+      </c>
+      <c r="L100" t="n">
+        <v>38</v>
+      </c>
+      <c r="M100" t="n">
+        <v>6</v>
+      </c>
+      <c r="N100" t="n">
+        <v>9</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>12</v>
+      </c>
+      <c r="R100" t="n">
+        <v>21</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
+        <v>167</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr"/>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
+      <c r="AQ100" t="inlineStr"/>
+      <c r="AR100" t="inlineStr"/>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AU100" t="inlineStr"/>
+      <c r="AV100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr"/>
+      <c r="AX100" t="inlineStr"/>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr"/>
+      <c r="BA100" t="inlineStr"/>
+      <c r="BB100" t="inlineStr"/>
+      <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr"/>
+      <c r="BM100" t="inlineStr"/>
+      <c r="BN100" t="inlineStr"/>
+      <c r="BO100" t="inlineStr"/>
+      <c r="BP100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>KU63vRwj</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wild horse pass stadium
+  chandler  az </t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>55</v>
+      </c>
+      <c r="L101" t="n">
+        <v>45</v>
+      </c>
+      <c r="M101" t="n">
+        <v>12</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>16</v>
+      </c>
+      <c r="R101" t="n">
+        <v>16</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="U101" t="n">
+        <v>167</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+      <c r="AQ101" t="inlineStr"/>
+      <c r="AR101" t="inlineStr"/>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AU101" t="inlineStr"/>
+      <c r="AV101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr"/>
+      <c r="BA101" t="inlineStr"/>
+      <c r="BB101" t="inlineStr"/>
+      <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr"/>
+      <c r="BM101" t="inlineStr"/>
+      <c r="BN101" t="inlineStr"/>
+      <c r="BO101" t="inlineStr"/>
+      <c r="BP101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>0pQWqmGS</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45466.04166666666</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corbyn m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F102" t="n">
+        <v>10176</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>59</v>
+      </c>
+      <c r="L102" t="n">
+        <v>41</v>
+      </c>
+      <c r="M102" t="n">
+        <v>8</v>
+      </c>
+      <c r="N102" t="n">
+        <v>16</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>16</v>
+      </c>
+      <c r="R102" t="n">
+        <v>12</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="U102" t="n">
+        <v>167</v>
+      </c>
+      <c r="V102" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
+      <c r="AQ102" t="inlineStr"/>
+      <c r="AR102" t="inlineStr"/>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr"/>
+      <c r="BA102" t="inlineStr"/>
+      <c r="BB102" t="inlineStr"/>
+      <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr"/>
+      <c r="BM102" t="inlineStr"/>
+      <c r="BN102" t="inlineStr"/>
+      <c r="BO102" t="inlineStr"/>
+      <c r="BP102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>plz8kini</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">matto j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3433</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>35</v>
+      </c>
+      <c r="L103" t="n">
+        <v>65</v>
+      </c>
+      <c r="M103" t="n">
+        <v>12</v>
+      </c>
+      <c r="N103" t="n">
+        <v>12</v>
+      </c>
+      <c r="O103" t="n">
+        <v>8</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>21</v>
+      </c>
+      <c r="R103" t="n">
+        <v>8</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="U103" t="n">
+        <v>167</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+      <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="inlineStr"/>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AU103" t="inlineStr"/>
+      <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr"/>
+      <c r="BA103" t="inlineStr"/>
+      <c r="BB103" t="inlineStr"/>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr"/>
+      <c r="BM103" t="inlineStr"/>
+      <c r="BN103" t="inlineStr"/>
+      <c r="BO103" t="inlineStr"/>
+      <c r="BP103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>AeXJnkW9</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45466</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">johnston k 
+  usa </t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lynn family stadium
+  louisville  ky </t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>15304</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>64</v>
+      </c>
+      <c r="L104" t="n">
+        <v>36</v>
+      </c>
+      <c r="M104" t="n">
+        <v>31</v>
+      </c>
+      <c r="N104" t="n">
+        <v>11</v>
+      </c>
+      <c r="O104" t="n">
+        <v>11</v>
+      </c>
+      <c r="P104" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>12</v>
+      </c>
+      <c r="R104" t="n">
+        <v>11</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="U104" t="n">
+        <v>167</v>
+      </c>
+      <c r="V104" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+      <c r="AQ104" t="inlineStr"/>
+      <c r="AR104" t="inlineStr"/>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr"/>
+      <c r="BA104" t="inlineStr"/>
+      <c r="BB104" t="inlineStr"/>
+      <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr"/>
+      <c r="BM104" t="inlineStr"/>
+      <c r="BN104" t="inlineStr"/>
+      <c r="BO104" t="inlineStr"/>
+      <c r="BP104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2gCbu7Oq</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hassan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wakemed soccer park
+  cary  nc </t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1996</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>64</v>
+      </c>
+      <c r="L105" t="n">
+        <v>36</v>
+      </c>
+      <c r="M105" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>22</v>
+      </c>
+      <c r="R105" t="n">
+        <v>22</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="U105" t="n">
+        <v>167</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
+      <c r="AQ105" t="inlineStr"/>
+      <c r="AR105" t="inlineStr"/>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr"/>
+      <c r="BA105" t="inlineStr"/>
+      <c r="BB105" t="inlineStr"/>
+      <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr"/>
+      <c r="BM105" t="inlineStr"/>
+      <c r="BN105" t="inlineStr"/>
+      <c r="BO105" t="inlineStr"/>
+      <c r="BP105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>OvZBlB1c</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45465.95833333334</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">surgan j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michael a  carroll stadium
+  indianapolis  in </t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>12111</v>
+      </c>
+      <c r="F106" t="n">
+        <v>9490</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>62</v>
+      </c>
+      <c r="L106" t="n">
+        <v>38</v>
+      </c>
+      <c r="M106" t="n">
+        <v>17</v>
+      </c>
+      <c r="N106" t="n">
+        <v>9</v>
+      </c>
+      <c r="O106" t="n">
+        <v>6</v>
+      </c>
+      <c r="P106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>9</v>
+      </c>
+      <c r="R106" t="n">
+        <v>11</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+      <c r="U106" t="n">
+        <v>167</v>
+      </c>
+      <c r="V106" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
+      <c r="AQ106" t="inlineStr"/>
+      <c r="AR106" t="inlineStr"/>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AU106" t="inlineStr"/>
+      <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr"/>
+      <c r="BA106" t="inlineStr"/>
+      <c r="BB106" t="inlineStr"/>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr"/>
+      <c r="BM106" t="inlineStr"/>
+      <c r="BN106" t="inlineStr"/>
+      <c r="BO106" t="inlineStr"/>
+      <c r="BP106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>hKMOo9oG</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45465.95833333334</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tattersall e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riccardo silva stadium
+  miami  fl </t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F107" t="n">
+        <v>846</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>38</v>
+      </c>
+      <c r="L107" t="n">
+        <v>62</v>
+      </c>
+      <c r="M107" t="n">
+        <v>9</v>
+      </c>
+      <c r="N107" t="n">
+        <v>19</v>
+      </c>
+      <c r="O107" t="n">
+        <v>4</v>
+      </c>
+      <c r="P107" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>14</v>
+      </c>
+      <c r="R107" t="n">
+        <v>10</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="U107" t="n">
+        <v>167</v>
+      </c>
+      <c r="V107" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+      <c r="AQ107" t="inlineStr"/>
+      <c r="AR107" t="inlineStr"/>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AU107" t="inlineStr"/>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr"/>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr"/>
+      <c r="BM107" t="inlineStr"/>
+      <c r="BN107" t="inlineStr"/>
+      <c r="BO107" t="inlineStr"/>
+      <c r="BP107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>6NQSpT0M</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45465.91666666666</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">montero r 
+  cos </t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardinale stadium
+  seaside  ca </t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4330</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>37</v>
+      </c>
+      <c r="L108" t="n">
+        <v>63</v>
+      </c>
+      <c r="M108" t="n">
+        <v>8</v>
+      </c>
+      <c r="N108" t="n">
+        <v>17</v>
+      </c>
+      <c r="O108" t="n">
+        <v>5</v>
+      </c>
+      <c r="P108" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>17</v>
+      </c>
+      <c r="R108" t="n">
+        <v>11</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="U108" t="n">
+        <v>167</v>
+      </c>
+      <c r="V108" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+      <c r="AQ108" t="inlineStr"/>
+      <c r="AR108" t="inlineStr"/>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr"/>
+      <c r="BA108" t="inlineStr"/>
+      <c r="BB108" t="inlineStr"/>
+      <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="inlineStr"/>
+      <c r="BM108" t="inlineStr"/>
+      <c r="BN108" t="inlineStr"/>
+      <c r="BO108" t="inlineStr"/>
+      <c r="BP108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19969,6 +19969,294 @@
       <c r="BO108" t="inlineStr"/>
       <c r="BP108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45469.85416666666</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bensalah n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beirne stadium
+  pawtucket  ri </t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5252</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3481</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>39</v>
+      </c>
+      <c r="L109" t="n">
+        <v>61</v>
+      </c>
+      <c r="M109" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>5</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>22</v>
+      </c>
+      <c r="R109" t="n">
+        <v>11</v>
+      </c>
+      <c r="S109" t="n">
+        <v>13</v>
+      </c>
+      <c r="T109" t="n">
+        <v>7</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="W109" t="n">
+        <v>167</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>56</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>270000</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr"/>
+      <c r="BA109" t="inlineStr"/>
+      <c r="BB109" t="inlineStr"/>
+      <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr"/>
+      <c r="BI109" t="inlineStr"/>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="inlineStr"/>
+      <c r="BM109" t="inlineStr"/>
+      <c r="BN109" t="inlineStr"/>
+      <c r="BO109" t="inlineStr"/>
+      <c r="BP109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45469.83333333334</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyworth stadium
+  hamtramck  mi </t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>7933</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6244</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>51</v>
+      </c>
+      <c r="L110" t="n">
+        <v>49</v>
+      </c>
+      <c r="M110" t="n">
+        <v>6</v>
+      </c>
+      <c r="N110" t="n">
+        <v>15</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>11</v>
+      </c>
+      <c r="R110" t="n">
+        <v>13</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="n">
+        <v>4</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="W110" t="n">
+        <v>167</v>
+      </c>
+      <c r="X110" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr"/>
+      <c r="AP110" t="inlineStr"/>
+      <c r="AQ110" t="inlineStr"/>
+      <c r="AR110" t="inlineStr"/>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AU110" t="inlineStr"/>
+      <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr"/>
+      <c r="BA110" t="inlineStr"/>
+      <c r="BB110" t="inlineStr"/>
+      <c r="BC110" t="inlineStr"/>
+      <c r="BD110" t="inlineStr"/>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr"/>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
+      <c r="BI110" t="inlineStr"/>
+      <c r="BJ110" t="inlineStr"/>
+      <c r="BK110" t="inlineStr"/>
+      <c r="BL110" t="inlineStr"/>
+      <c r="BM110" t="inlineStr"/>
+      <c r="BN110" t="inlineStr"/>
+      <c r="BO110" t="inlineStr"/>
+      <c r="BP110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20257,6 +20257,4350 @@
       <c r="BO110" t="inlineStr"/>
       <c r="BP110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>54</v>
+      </c>
+      <c r="L111" t="n">
+        <v>46</v>
+      </c>
+      <c r="M111" t="n">
+        <v>22</v>
+      </c>
+      <c r="N111" t="n">
+        <v>11</v>
+      </c>
+      <c r="O111" t="n">
+        <v>11</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>10</v>
+      </c>
+      <c r="R111" t="n">
+        <v>11</v>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="W111" t="n">
+        <v>167</v>
+      </c>
+      <c r="X111" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AE111" t="n">
+        <v>29.36363636363636</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>3952272.727272727</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>74.18181818181819</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>1785500</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>23.82608695652174</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>177.8260869565217</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>66.91304347826087</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>2334782.608695652</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>73.91304347826087</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>22.1304347826087</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>181</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>60.1304347826087</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>881956.5217391305</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>68.91304347826087</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>189</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>68</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>179</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>118</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>64</v>
+      </c>
+      <c r="L112" t="n">
+        <v>36</v>
+      </c>
+      <c r="M112" t="n">
+        <v>25</v>
+      </c>
+      <c r="N112" t="n">
+        <v>6</v>
+      </c>
+      <c r="O112" t="n">
+        <v>11</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>9</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7</v>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="W112" t="n">
+        <v>167</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE112" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>2979545.454545455</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>64.81818181818181</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>1083636.363636364</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>26.17391304347826</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>180.3478260869565</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>66.65217391304348</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>1332826.086956522</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>69.39130434782609</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>23.42857142857143</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>60.71428571428572</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>707142.8571428572</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>130</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>120</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stanford stadium
+  stanford  ca </t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>50424</v>
+      </c>
+      <c r="F113" t="n">
+        <v>40844</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>42</v>
+      </c>
+      <c r="L113" t="n">
+        <v>58</v>
+      </c>
+      <c r="M113" t="n">
+        <v>18</v>
+      </c>
+      <c r="N113" t="n">
+        <v>13</v>
+      </c>
+      <c r="O113" t="n">
+        <v>6</v>
+      </c>
+      <c r="P113" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>11</v>
+      </c>
+      <c r="R113" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="W113" t="n">
+        <v>167</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>2637000</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>179.2222222222222</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>2897222.222222222</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>1585000</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>23.36363636363636</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>178.7727272727273</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>3439772.727272727</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>134</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>175</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>73</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>52</v>
+      </c>
+      <c r="L114" t="n">
+        <v>48</v>
+      </c>
+      <c r="M114" t="n">
+        <v>13</v>
+      </c>
+      <c r="N114" t="n">
+        <v>8</v>
+      </c>
+      <c r="O114" t="n">
+        <v>6</v>
+      </c>
+      <c r="P114" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>10</v>
+      </c>
+      <c r="R114" t="n">
+        <v>17</v>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="W114" t="n">
+        <v>167</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AE114" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>2216666.666666667</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2245454.545454545</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>177.95</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>2944250</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1533125</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>69.41666666666667</v>
+      </c>
+      <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="inlineStr"/>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr"/>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="n">
+        <v>27</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>343</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>9275000</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F115" t="n">
+        <v>24662</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>60</v>
+      </c>
+      <c r="L115" t="n">
+        <v>40</v>
+      </c>
+      <c r="M115" t="n">
+        <v>14</v>
+      </c>
+      <c r="N115" t="n">
+        <v>11</v>
+      </c>
+      <c r="O115" t="n">
+        <v>9</v>
+      </c>
+      <c r="P115" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>11</v>
+      </c>
+      <c r="R115" t="n">
+        <v>9</v>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="W115" t="n">
+        <v>167</v>
+      </c>
+      <c r="X115" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE115" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>2332500</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>23.73684210526316</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>179</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>64.89473684210526</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>1530263.157894737</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>70.52631578947368</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>20.71428571428572</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>183</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>57.71428571428572</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>137</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>137</v>
+      </c>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
+      <c r="BM115" t="inlineStr"/>
+      <c r="BN115" t="inlineStr"/>
+      <c r="BO115" t="inlineStr"/>
+      <c r="BP115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F116" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>51</v>
+      </c>
+      <c r="L116" t="n">
+        <v>49</v>
+      </c>
+      <c r="M116" t="n">
+        <v>13</v>
+      </c>
+      <c r="N116" t="n">
+        <v>5</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2</v>
+      </c>
+      <c r="P116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>16</v>
+      </c>
+      <c r="R116" t="n">
+        <v>14</v>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="W116" t="n">
+        <v>167</v>
+      </c>
+      <c r="X116" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AE116" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1529545.454545455</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>3281363.636363636</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1958000</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>24.26086956521739</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>181.3913043478261</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>61.8695652173913</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>1705000</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>67.1304347826087</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>173.3333333333333</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>405</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>25575000</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>452</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>330</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>8155000</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F117" t="n">
+        <v>15321</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>66</v>
+      </c>
+      <c r="L117" t="n">
+        <v>34</v>
+      </c>
+      <c r="M117" t="n">
+        <v>16</v>
+      </c>
+      <c r="N117" t="n">
+        <v>9</v>
+      </c>
+      <c r="O117" t="n">
+        <v>4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>8</v>
+      </c>
+      <c r="R117" t="n">
+        <v>9</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="W117" t="n">
+        <v>167</v>
+      </c>
+      <c r="X117" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE117" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1959545.454545455</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>1932500</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>178.7619047619048</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>1.095238095238095</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>62.38095238095238</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1095952.380952381</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>68.38095238095238</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>26.1875</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>63.6875</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>1008437.5</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>175.3333333333333</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>195</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>211</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>198</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2275000</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F118" t="n">
+        <v>30109</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>52</v>
+      </c>
+      <c r="L118" t="n">
+        <v>48</v>
+      </c>
+      <c r="M118" t="n">
+        <v>11</v>
+      </c>
+      <c r="N118" t="n">
+        <v>14</v>
+      </c>
+      <c r="O118" t="n">
+        <v>5</v>
+      </c>
+      <c r="P118" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>2</v>
+      </c>
+      <c r="R118" t="n">
+        <v>11</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="W118" t="n">
+        <v>167</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AE118" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>3286363.636363636</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>70.90909090909091</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>4382500</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>182.4736842105263</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>62.63157894736842</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>636315.7894736842</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>64.36842105263158</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>22.47368421052632</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>186.4736842105263</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>64.31578947368421</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1206578.947368421</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>72.36842105263158</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>392</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>411</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>385</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>71125000</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F119" t="n">
+        <v>18722</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>51</v>
+      </c>
+      <c r="L119" t="n">
+        <v>49</v>
+      </c>
+      <c r="M119" t="n">
+        <v>15</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>2</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>16</v>
+      </c>
+      <c r="R119" t="n">
+        <v>19</v>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="W119" t="n">
+        <v>167</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE119" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1251000</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2372500</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>178.7619047619048</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>62.38095238095238</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>764285.7142857143</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>66.95238095238095</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>29.70588235294118</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>179.0588235294118</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>65.35294117647059</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>762352.9411764706</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>65.82352941176471</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>208</v>
+      </c>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
+      <c r="BO119" t="inlineStr"/>
+      <c r="BP119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F120" t="n">
+        <v>42568</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>48</v>
+      </c>
+      <c r="L120" t="n">
+        <v>52</v>
+      </c>
+      <c r="M120" t="n">
+        <v>10</v>
+      </c>
+      <c r="N120" t="n">
+        <v>13</v>
+      </c>
+      <c r="O120" t="n">
+        <v>5</v>
+      </c>
+      <c r="P120" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>16</v>
+      </c>
+      <c r="R120" t="n">
+        <v>10</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="W120" t="n">
+        <v>167</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AE120" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>5208181.818181818</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>3260000</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1089285.714285714</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>70.0952380952381</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>64</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1546000</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>176</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>209</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>218</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>331</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>5465000</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F121" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>61</v>
+      </c>
+      <c r="L121" t="n">
+        <v>39</v>
+      </c>
+      <c r="M121" t="n">
+        <v>13</v>
+      </c>
+      <c r="N121" t="n">
+        <v>7</v>
+      </c>
+      <c r="O121" t="n">
+        <v>6</v>
+      </c>
+      <c r="P121" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>10</v>
+      </c>
+      <c r="R121" t="n">
+        <v>10</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="W121" t="n">
+        <v>167</v>
+      </c>
+      <c r="X121" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AE121" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>178.2727272727273</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1409090.909090909</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2577777.777777778</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>74.22222222222223</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>180.7894736842105</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>66.36842105263158</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>1696842.105263158</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>72.31578947368421</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>180.5454545454545</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>64.90909090909091</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>2269090.909090909</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>330</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>5850000</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>350</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>351</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>12675000</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F122" t="n">
+        <v>25004</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>5</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>42</v>
+      </c>
+      <c r="L122" t="n">
+        <v>58</v>
+      </c>
+      <c r="M122" t="n">
+        <v>8</v>
+      </c>
+      <c r="N122" t="n">
+        <v>20</v>
+      </c>
+      <c r="O122" t="n">
+        <v>6</v>
+      </c>
+      <c r="P122" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>15</v>
+      </c>
+      <c r="R122" t="n">
+        <v>8</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="W122" t="n">
+        <v>167</v>
+      </c>
+      <c r="X122" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AE122" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1363888.888888889</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>181</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>3790909.090909091</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>26.73913043478261</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>180.8260869565217</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>66.39130434782609</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>1115217.391304348</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>70.39130434782609</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>1323750</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>143</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>146</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>37</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>63</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F123" t="n">
+        <v>18315</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>65</v>
+      </c>
+      <c r="L123" t="n">
+        <v>35</v>
+      </c>
+      <c r="M123" t="n">
+        <v>23</v>
+      </c>
+      <c r="N123" t="n">
+        <v>8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>4</v>
+      </c>
+      <c r="P123" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>16</v>
+      </c>
+      <c r="R123" t="n">
+        <v>11</v>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="W123" t="n">
+        <v>167</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="n">
+        <v>22.36363636363636</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>180.9090909090909</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1524545.454545455</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1124000</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>3894500</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>22.81818181818182</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>61.45454545454545</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>235</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>287</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>375</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>6375000</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>54</v>
+      </c>
+      <c r="L124" t="n">
+        <v>46</v>
+      </c>
+      <c r="M124" t="n">
+        <v>14</v>
+      </c>
+      <c r="N124" t="n">
+        <v>14</v>
+      </c>
+      <c r="O124" t="n">
+        <v>7</v>
+      </c>
+      <c r="P124" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>12</v>
+      </c>
+      <c r="R124" t="n">
+        <v>10</v>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="W124" t="n">
+        <v>167</v>
+      </c>
+      <c r="X124" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE124" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1577222.222222222</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2348500</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>21.85714285714286</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>182.2857142857143</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>62.35714285714285</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1065714.285714286</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>70.64285714285714</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1.238095238095238</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>62.47619047619047</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>2752857.142857143</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>68.47619047619048</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>375000</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>65</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>388</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>8565000</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hassan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9249</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>53</v>
+      </c>
+      <c r="L125" t="n">
+        <v>47</v>
+      </c>
+      <c r="M125" t="n">
+        <v>12</v>
+      </c>
+      <c r="N125" t="n">
+        <v>8</v>
+      </c>
+      <c r="O125" t="n">
+        <v>5</v>
+      </c>
+      <c r="P125" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>167</v>
+      </c>
+      <c r="X125" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="inlineStr"/>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr"/>
+      <c r="AR125" t="inlineStr"/>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AU125" t="inlineStr"/>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr"/>
+      <c r="BA125" t="inlineStr"/>
+      <c r="BB125" t="inlineStr"/>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
+      <c r="BO125" t="inlineStr"/>
+      <c r="BP125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cashman field
+  las vegas  nv </t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1893</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>52</v>
+      </c>
+      <c r="L126" t="n">
+        <v>48</v>
+      </c>
+      <c r="M126" t="n">
+        <v>8</v>
+      </c>
+      <c r="N126" t="n">
+        <v>6</v>
+      </c>
+      <c r="O126" t="n">
+        <v>3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>20</v>
+      </c>
+      <c r="R126" t="n">
+        <v>13</v>
+      </c>
+      <c r="S126" t="n">
+        <v>8</v>
+      </c>
+      <c r="T126" t="n">
+        <v>5</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="W126" t="n">
+        <v>167</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="inlineStr"/>
+      <c r="AK126" t="inlineStr"/>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr"/>
+      <c r="AO126" t="inlineStr"/>
+      <c r="AP126" t="inlineStr"/>
+      <c r="AQ126" t="inlineStr"/>
+      <c r="AR126" t="inlineStr"/>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AU126" t="inlineStr"/>
+      <c r="AV126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr"/>
+      <c r="BA126" t="inlineStr"/>
+      <c r="BB126" t="inlineStr"/>
+      <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
+      <c r="BO126" t="inlineStr"/>
+      <c r="BP126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45472.95833333334</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F127" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>51</v>
+      </c>
+      <c r="L127" t="n">
+        <v>49</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>4</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6</v>
+      </c>
+      <c r="S127" t="n">
+        <v>2</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="W127" t="n">
+        <v>167</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="inlineStr"/>
+      <c r="AK127" t="inlineStr"/>
+      <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr"/>
+      <c r="AN127" t="inlineStr"/>
+      <c r="AO127" t="inlineStr"/>
+      <c r="AP127" t="inlineStr"/>
+      <c r="AQ127" t="inlineStr"/>
+      <c r="AR127" t="inlineStr"/>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AU127" t="inlineStr"/>
+      <c r="AV127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr"/>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr"/>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+      <c r="BM127" t="inlineStr"/>
+      <c r="BN127" t="inlineStr"/>
+      <c r="BO127" t="inlineStr"/>
+      <c r="BP127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45472.91666666666</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F128" t="n">
+        <v>8023</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>60</v>
+      </c>
+      <c r="L128" t="n">
+        <v>40</v>
+      </c>
+      <c r="M128" t="n">
+        <v>16</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" t="n">
+        <v>6</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>12</v>
+      </c>
+      <c r="R128" t="n">
+        <v>9</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="n">
+        <v>8</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="W128" t="n">
+        <v>167</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr"/>
+      <c r="AK128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="inlineStr"/>
+      <c r="AP128" t="inlineStr"/>
+      <c r="AQ128" t="inlineStr"/>
+      <c r="AR128" t="inlineStr"/>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AU128" t="inlineStr"/>
+      <c r="AV128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr"/>
+      <c r="BA128" t="inlineStr"/>
+      <c r="BB128" t="inlineStr"/>
+      <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+      <c r="BM128" t="inlineStr"/>
+      <c r="BN128" t="inlineStr"/>
+      <c r="BO128" t="inlineStr"/>
+      <c r="BP128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45472.91666666666</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corrigan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota field
+  san antonio  tx </t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F129" t="n">
+        <v>6625</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>68</v>
+      </c>
+      <c r="L129" t="n">
+        <v>32</v>
+      </c>
+      <c r="M129" t="n">
+        <v>17</v>
+      </c>
+      <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="n">
+        <v>5</v>
+      </c>
+      <c r="P129" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>16</v>
+      </c>
+      <c r="R129" t="n">
+        <v>15</v>
+      </c>
+      <c r="S129" t="n">
+        <v>6</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="W129" t="n">
+        <v>167</v>
+      </c>
+      <c r="X129" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="inlineStr"/>
+      <c r="AK129" t="inlineStr"/>
+      <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr"/>
+      <c r="AO129" t="inlineStr"/>
+      <c r="AP129" t="inlineStr"/>
+      <c r="AQ129" t="inlineStr"/>
+      <c r="AR129" t="inlineStr"/>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AU129" t="inlineStr"/>
+      <c r="AV129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr"/>
+      <c r="BA129" t="inlineStr"/>
+      <c r="BB129" t="inlineStr"/>
+      <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+      <c r="BM129" t="inlineStr"/>
+      <c r="BN129" t="inlineStr"/>
+      <c r="BO129" t="inlineStr"/>
+      <c r="BP129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">encarnacion j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>49</v>
+      </c>
+      <c r="L130" t="n">
+        <v>51</v>
+      </c>
+      <c r="M130" t="n">
+        <v>13</v>
+      </c>
+      <c r="N130" t="n">
+        <v>20</v>
+      </c>
+      <c r="O130" t="n">
+        <v>6</v>
+      </c>
+      <c r="P130" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>5</v>
+      </c>
+      <c r="R130" t="n">
+        <v>14</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="n">
+        <v>9</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="W130" t="n">
+        <v>167</v>
+      </c>
+      <c r="X130" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="inlineStr"/>
+      <c r="AK130" t="inlineStr"/>
+      <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr"/>
+      <c r="AN130" t="inlineStr"/>
+      <c r="AO130" t="inlineStr"/>
+      <c r="AP130" t="inlineStr"/>
+      <c r="AQ130" t="inlineStr"/>
+      <c r="AR130" t="inlineStr"/>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AU130" t="inlineStr"/>
+      <c r="AV130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr"/>
+      <c r="AX130" t="inlineStr"/>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr"/>
+      <c r="BA130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr"/>
+      <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
+      <c r="BM130" t="inlineStr"/>
+      <c r="BN130" t="inlineStr"/>
+      <c r="BO130" t="inlineStr"/>
+      <c r="BP130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arroyo l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segra field
+  leesburg  va </t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3076</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>44</v>
+      </c>
+      <c r="L131" t="n">
+        <v>56</v>
+      </c>
+      <c r="M131" t="n">
+        <v>23</v>
+      </c>
+      <c r="N131" t="n">
+        <v>17</v>
+      </c>
+      <c r="O131" t="n">
+        <v>8</v>
+      </c>
+      <c r="P131" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>10</v>
+      </c>
+      <c r="R131" t="n">
+        <v>13</v>
+      </c>
+      <c r="S131" t="n">
+        <v>6</v>
+      </c>
+      <c r="T131" t="n">
+        <v>9</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="W131" t="n">
+        <v>167</v>
+      </c>
+      <c r="X131" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="inlineStr"/>
+      <c r="AK131" t="inlineStr"/>
+      <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr"/>
+      <c r="AN131" t="inlineStr"/>
+      <c r="AO131" t="inlineStr"/>
+      <c r="AP131" t="inlineStr"/>
+      <c r="AQ131" t="inlineStr"/>
+      <c r="AR131" t="inlineStr"/>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AU131" t="inlineStr"/>
+      <c r="AV131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
+      <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr"/>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
+      <c r="BM131" t="inlineStr"/>
+      <c r="BN131" t="inlineStr"/>
+      <c r="BO131" t="inlineStr"/>
+      <c r="BP131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>45472.83333333334</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nichols a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riccardo silva stadium
+  miami  fl </t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1077</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>42</v>
+      </c>
+      <c r="L132" t="n">
+        <v>58</v>
+      </c>
+      <c r="M132" t="n">
+        <v>13</v>
+      </c>
+      <c r="N132" t="n">
+        <v>15</v>
+      </c>
+      <c r="O132" t="n">
+        <v>2</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>16</v>
+      </c>
+      <c r="R132" t="n">
+        <v>12</v>
+      </c>
+      <c r="S132" t="n">
+        <v>2</v>
+      </c>
+      <c r="T132" t="n">
+        <v>6</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="W132" t="n">
+        <v>167</v>
+      </c>
+      <c r="X132" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr"/>
+      <c r="AJ132" t="inlineStr"/>
+      <c r="AK132" t="inlineStr"/>
+      <c r="AL132" t="inlineStr"/>
+      <c r="AM132" t="inlineStr"/>
+      <c r="AN132" t="inlineStr"/>
+      <c r="AO132" t="inlineStr"/>
+      <c r="AP132" t="inlineStr"/>
+      <c r="AQ132" t="inlineStr"/>
+      <c r="AR132" t="inlineStr"/>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AU132" t="inlineStr"/>
+      <c r="AV132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr"/>
+      <c r="AX132" t="inlineStr"/>
+      <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr"/>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="inlineStr"/>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
+      <c r="BM132" t="inlineStr"/>
+      <c r="BN132" t="inlineStr"/>
+      <c r="BO132" t="inlineStr"/>
+      <c r="BP132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45471.89583333334</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheer j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">autozone park
+  memphis  tn </t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2775</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>43</v>
+      </c>
+      <c r="L133" t="n">
+        <v>57</v>
+      </c>
+      <c r="M133" t="n">
+        <v>15</v>
+      </c>
+      <c r="N133" t="n">
+        <v>9</v>
+      </c>
+      <c r="O133" t="n">
+        <v>11</v>
+      </c>
+      <c r="P133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>14</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6</v>
+      </c>
+      <c r="S133" t="n">
+        <v>6</v>
+      </c>
+      <c r="T133" t="n">
+        <v>7</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="W133" t="n">
+        <v>167</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr"/>
+      <c r="AJ133" t="inlineStr"/>
+      <c r="AK133" t="inlineStr"/>
+      <c r="AL133" t="inlineStr"/>
+      <c r="AM133" t="inlineStr"/>
+      <c r="AN133" t="inlineStr"/>
+      <c r="AO133" t="inlineStr"/>
+      <c r="AP133" t="inlineStr"/>
+      <c r="AQ133" t="inlineStr"/>
+      <c r="AR133" t="inlineStr"/>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AU133" t="inlineStr"/>
+      <c r="AV133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr"/>
+      <c r="AX133" t="inlineStr"/>
+      <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr"/>
+      <c r="BA133" t="inlineStr"/>
+      <c r="BB133" t="inlineStr"/>
+      <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
+      <c r="BH133" t="inlineStr"/>
+      <c r="BI133" t="inlineStr"/>
+      <c r="BJ133" t="inlineStr"/>
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="inlineStr"/>
+      <c r="BM133" t="inlineStr"/>
+      <c r="BN133" t="inlineStr"/>
+      <c r="BO133" t="inlineStr"/>
+      <c r="BP133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flores g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3876</v>
+      </c>
+      <c r="G134" t="n">
+        <v>5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>70</v>
+      </c>
+      <c r="L134" t="n">
+        <v>30</v>
+      </c>
+      <c r="M134" t="n">
+        <v>25</v>
+      </c>
+      <c r="N134" t="n">
+        <v>9</v>
+      </c>
+      <c r="O134" t="n">
+        <v>9</v>
+      </c>
+      <c r="P134" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>14</v>
+      </c>
+      <c r="R134" t="n">
+        <v>12</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="n">
+        <v>9</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="W134" t="n">
+        <v>167</v>
+      </c>
+      <c r="X134" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="inlineStr"/>
+      <c r="AK134" t="inlineStr"/>
+      <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr"/>
+      <c r="AO134" t="inlineStr"/>
+      <c r="AP134" t="inlineStr"/>
+      <c r="AQ134" t="inlineStr"/>
+      <c r="AR134" t="inlineStr"/>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AU134" t="inlineStr"/>
+      <c r="AV134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr"/>
+      <c r="AX134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr"/>
+      <c r="BA134" t="inlineStr"/>
+      <c r="BB134" t="inlineStr"/>
+      <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
+      <c r="BI134" t="inlineStr"/>
+      <c r="BJ134" t="inlineStr"/>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="inlineStr"/>
+      <c r="BM134" t="inlineStr"/>
+      <c r="BN134" t="inlineStr"/>
+      <c r="BO134" t="inlineStr"/>
+      <c r="BP134" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24601,6 +24601,8174 @@
       <c r="BO134" t="inlineStr"/>
       <c r="BP134" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F135" t="n">
+        <v>21522</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>47</v>
+      </c>
+      <c r="L135" t="n">
+        <v>53</v>
+      </c>
+      <c r="M135" t="n">
+        <v>19</v>
+      </c>
+      <c r="N135" t="n">
+        <v>7</v>
+      </c>
+      <c r="O135" t="n">
+        <v>10</v>
+      </c>
+      <c r="P135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>17</v>
+      </c>
+      <c r="R135" t="n">
+        <v>14</v>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="W135" t="n">
+        <v>167</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AE135" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2052500</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1914090.909090909</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>25.10526315789474</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>181.3157894736842</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>64</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>1603421.052631579</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>70.15789473684211</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>24.88235294117647</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>179.8235294117647</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>62.76470588235294</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>925882.3529411765</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>67.76470588235294</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>128</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>131</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>124</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F136" t="n">
+        <v>19453</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>48</v>
+      </c>
+      <c r="L136" t="n">
+        <v>52</v>
+      </c>
+      <c r="M136" t="n">
+        <v>17</v>
+      </c>
+      <c r="N136" t="n">
+        <v>12</v>
+      </c>
+      <c r="O136" t="n">
+        <v>10</v>
+      </c>
+      <c r="P136" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>16</v>
+      </c>
+      <c r="R136" t="n">
+        <v>12</v>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="W136" t="n">
+        <v>167</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AE136" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2234090.909090909</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2719000</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>181.6818181818182</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>65.36363636363636</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>1539545.454545455</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>435000</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>64</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>407</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>10475000</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>430</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>421</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>14775000</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F137" t="n">
+        <v>19684</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>55</v>
+      </c>
+      <c r="L137" t="n">
+        <v>45</v>
+      </c>
+      <c r="M137" t="n">
+        <v>16</v>
+      </c>
+      <c r="N137" t="n">
+        <v>5</v>
+      </c>
+      <c r="O137" t="n">
+        <v>4</v>
+      </c>
+      <c r="P137" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" t="n">
+        <v>13</v>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="W137" t="n">
+        <v>167</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE137" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2452500</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>71</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>174.3571428571429</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>63.35714285714285</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>928571.4285714285</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>69.07142857142857</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>175.9090909090909</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>1360227.272727273</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>185.7142857142857</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>443</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>7310000</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>464</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>345</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F138" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>55</v>
+      </c>
+      <c r="L138" t="n">
+        <v>45</v>
+      </c>
+      <c r="M138" t="n">
+        <v>21</v>
+      </c>
+      <c r="N138" t="n">
+        <v>8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>8</v>
+      </c>
+      <c r="P138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>15</v>
+      </c>
+      <c r="R138" t="n">
+        <v>12</v>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="W138" t="n">
+        <v>167</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>2007500</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1402000</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>23.82352941176471</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>184.8823529411765</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>62.64705882352941</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1061764.705882353</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>68.58823529411765</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>68.04166666666667</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>2453125</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>71.41666666666667</v>
+      </c>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="inlineStr"/>
+      <c r="BJ138" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>125</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F139" t="n">
+        <v>20171</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>46</v>
+      </c>
+      <c r="L139" t="n">
+        <v>54</v>
+      </c>
+      <c r="M139" t="n">
+        <v>12</v>
+      </c>
+      <c r="N139" t="n">
+        <v>17</v>
+      </c>
+      <c r="O139" t="n">
+        <v>5</v>
+      </c>
+      <c r="P139" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>5</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7</v>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="W139" t="n">
+        <v>167</v>
+      </c>
+      <c r="X139" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1488636.363636364</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>180.7272727272727</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1274090.909090909</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>27.82352941176471</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>181.5294117647059</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>66.94117647058823</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1008823.529411765</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>69.05882352941177</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>176.3888888888889</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>64.94444444444444</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>959722.2222222222</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>143</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>146</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>172</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>67</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F140" t="n">
+        <v>47218</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>48</v>
+      </c>
+      <c r="L140" t="n">
+        <v>52</v>
+      </c>
+      <c r="M140" t="n">
+        <v>13</v>
+      </c>
+      <c r="N140" t="n">
+        <v>8</v>
+      </c>
+      <c r="O140" t="n">
+        <v>3</v>
+      </c>
+      <c r="P140" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>13</v>
+      </c>
+      <c r="R140" t="n">
+        <v>11</v>
+      </c>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="W140" t="n">
+        <v>167</v>
+      </c>
+      <c r="X140" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AE140" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1893181.818181818</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>4250000</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>25.61538461538462</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>181.7692307692308</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>67</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2489615.384615385</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>72.15384615384616</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>184</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>63.61111111111111</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1086111.111111111</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>136</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>176</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>391</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>97625000</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F141" t="n">
+        <v>16716</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>50</v>
+      </c>
+      <c r="L141" t="n">
+        <v>50</v>
+      </c>
+      <c r="M141" t="n">
+        <v>15</v>
+      </c>
+      <c r="N141" t="n">
+        <v>12</v>
+      </c>
+      <c r="O141" t="n">
+        <v>5</v>
+      </c>
+      <c r="P141" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>9</v>
+      </c>
+      <c r="R141" t="n">
+        <v>13</v>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>MFwJSk8d</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="W141" t="n">
+        <v>167</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AE141" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>180.8181818181818</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>67.72727272727273</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>3667727.272727273</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>21.18181818181818</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>59.81818181818182</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>920000</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>70.72727272727273</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>25.60869565217391</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>180.9565217391304</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>63.39130434782609</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>67.08695652173913</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>316</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>354</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>185</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2055000</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F142" t="n">
+        <v>18209</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>49</v>
+      </c>
+      <c r="L142" t="n">
+        <v>51</v>
+      </c>
+      <c r="M142" t="n">
+        <v>16</v>
+      </c>
+      <c r="N142" t="n">
+        <v>11</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7</v>
+      </c>
+      <c r="P142" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>10</v>
+      </c>
+      <c r="R142" t="n">
+        <v>13</v>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="W142" t="n">
+        <v>167</v>
+      </c>
+      <c r="X142" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AE142" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1746875</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>23.18181818181818</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>176.7272727272727</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>66.45454545454545</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1277500</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>64.83333333333333</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1448541.666666667</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>71.79166666666667</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>375000</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>65</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>191</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F143" t="n">
+        <v>23877</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>56</v>
+      </c>
+      <c r="L143" t="n">
+        <v>44</v>
+      </c>
+      <c r="M143" t="n">
+        <v>11</v>
+      </c>
+      <c r="N143" t="n">
+        <v>14</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>10</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7</v>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="W143" t="n">
+        <v>167</v>
+      </c>
+      <c r="X143" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE143" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>3224500</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2372500</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>178.7222222222222</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>62.77777777777778</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>797500</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>26.04545454545455</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>177.3181818181818</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>67.13636363636364</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>3535909.090909091</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>117</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>990000</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>129</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>106</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>615000</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>57</v>
+      </c>
+      <c r="L144" t="n">
+        <v>43</v>
+      </c>
+      <c r="M144" t="n">
+        <v>20</v>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
+        <v>7</v>
+      </c>
+      <c r="P144" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>8</v>
+      </c>
+      <c r="R144" t="n">
+        <v>17</v>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>167</v>
+      </c>
+      <c r="X144" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE144" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>3790909.090909091</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>66.90909090909091</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>3061818.181818182</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>63.61111111111111</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>1953055.555555556</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>70.05555555555556</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>29.13333333333333</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>793333.3333333334</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>66.26666666666667</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>37</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>185</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>GUF0eJEs</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheer j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F145" t="n">
+        <v>8988</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>47</v>
+      </c>
+      <c r="L145" t="n">
+        <v>53</v>
+      </c>
+      <c r="M145" t="n">
+        <v>15</v>
+      </c>
+      <c r="N145" t="n">
+        <v>11</v>
+      </c>
+      <c r="O145" t="n">
+        <v>5</v>
+      </c>
+      <c r="P145" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>14</v>
+      </c>
+      <c r="R145" t="n">
+        <v>12</v>
+      </c>
+      <c r="S145" t="n">
+        <v>11</v>
+      </c>
+      <c r="T145" t="n">
+        <v>6</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="W145" t="n">
+        <v>167</v>
+      </c>
+      <c r="X145" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="inlineStr"/>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr"/>
+      <c r="AP145" t="inlineStr"/>
+      <c r="AQ145" t="inlineStr"/>
+      <c r="AR145" t="inlineStr"/>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AU145" t="inlineStr"/>
+      <c r="AV145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr"/>
+      <c r="AX145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr"/>
+      <c r="BA145" t="inlineStr"/>
+      <c r="BB145" t="inlineStr"/>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr"/>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="inlineStr"/>
+      <c r="BM145" t="inlineStr"/>
+      <c r="BN145" t="inlineStr"/>
+      <c r="BO145" t="inlineStr"/>
+      <c r="BP145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>v9OYaa6Q</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>45476.91666666666</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F146" t="n">
+        <v>12147</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>58</v>
+      </c>
+      <c r="L146" t="n">
+        <v>42</v>
+      </c>
+      <c r="M146" t="n">
+        <v>19</v>
+      </c>
+      <c r="N146" t="n">
+        <v>7</v>
+      </c>
+      <c r="O146" t="n">
+        <v>4</v>
+      </c>
+      <c r="P146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>15</v>
+      </c>
+      <c r="R146" t="n">
+        <v>11</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="n">
+        <v>10</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>167</v>
+      </c>
+      <c r="X146" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="inlineStr"/>
+      <c r="AK146" t="inlineStr"/>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="inlineStr"/>
+      <c r="AP146" t="inlineStr"/>
+      <c r="AQ146" t="inlineStr"/>
+      <c r="AR146" t="inlineStr"/>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AU146" t="inlineStr"/>
+      <c r="AV146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr"/>
+      <c r="AX146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr"/>
+      <c r="BA146" t="inlineStr"/>
+      <c r="BB146" t="inlineStr"/>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
+      <c r="BI146" t="inlineStr"/>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="inlineStr"/>
+      <c r="BM146" t="inlineStr"/>
+      <c r="BN146" t="inlineStr"/>
+      <c r="BO146" t="inlineStr"/>
+      <c r="BP146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>pnPU0uiK</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">matto j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segra field
+  leesburg  va </t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3789</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>49</v>
+      </c>
+      <c r="L147" t="n">
+        <v>51</v>
+      </c>
+      <c r="M147" t="n">
+        <v>17</v>
+      </c>
+      <c r="N147" t="n">
+        <v>8</v>
+      </c>
+      <c r="O147" t="n">
+        <v>10</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>9</v>
+      </c>
+      <c r="R147" t="n">
+        <v>8</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4</v>
+      </c>
+      <c r="T147" t="n">
+        <v>5</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>167</v>
+      </c>
+      <c r="X147" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr"/>
+      <c r="AP147" t="inlineStr"/>
+      <c r="AQ147" t="inlineStr"/>
+      <c r="AR147" t="inlineStr"/>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AU147" t="inlineStr"/>
+      <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr"/>
+      <c r="BA147" t="inlineStr"/>
+      <c r="BB147" t="inlineStr"/>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
+      <c r="BI147" t="inlineStr"/>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="inlineStr"/>
+      <c r="BM147" t="inlineStr"/>
+      <c r="BN147" t="inlineStr"/>
+      <c r="BO147" t="inlineStr"/>
+      <c r="BP147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45477.98611111111</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rose bowl
+  pasadena  ca </t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>92542</v>
+      </c>
+      <c r="F148" t="n">
+        <v>70076</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>57</v>
+      </c>
+      <c r="L148" t="n">
+        <v>43</v>
+      </c>
+      <c r="M148" t="n">
+        <v>10</v>
+      </c>
+      <c r="N148" t="n">
+        <v>23</v>
+      </c>
+      <c r="O148" t="n">
+        <v>4</v>
+      </c>
+      <c r="P148" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>7</v>
+      </c>
+      <c r="R148" t="n">
+        <v>14</v>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>167</v>
+      </c>
+      <c r="X148" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>178.7777777777778</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>4497222.222222222</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>29.36363636363636</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>3952272.727272727</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>74.18181818181819</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>24.89473684210526</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>179.2631578947368</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>65.15789473684211</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>179.5714285714286</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>66.57142857142857</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>1333928.571428571</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>129</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F149" t="n">
+        <v>18183</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>58</v>
+      </c>
+      <c r="L149" t="n">
+        <v>42</v>
+      </c>
+      <c r="M149" t="n">
+        <v>13</v>
+      </c>
+      <c r="N149" t="n">
+        <v>6</v>
+      </c>
+      <c r="O149" t="n">
+        <v>4</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>5</v>
+      </c>
+      <c r="R149" t="n">
+        <v>12</v>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="W149" t="n">
+        <v>167</v>
+      </c>
+      <c r="X149" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE149" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1825500</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>988500</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>21.23076923076923</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>181.7692307692308</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>57.92307692307692</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>491923.0769230769</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>69.07692307692308</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>27.08333333333333</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>179.9166666666667</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>66.45833333333333</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1360416.666666667</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>68.54166666666667</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>180</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>3040000</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>212</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>200</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F150" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>62</v>
+      </c>
+      <c r="L150" t="n">
+        <v>38</v>
+      </c>
+      <c r="M150" t="n">
+        <v>17</v>
+      </c>
+      <c r="N150" t="n">
+        <v>12</v>
+      </c>
+      <c r="O150" t="n">
+        <v>5</v>
+      </c>
+      <c r="P150" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>17</v>
+      </c>
+      <c r="R150" t="n">
+        <v>10</v>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="W150" t="n">
+        <v>167</v>
+      </c>
+      <c r="X150" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE150" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>178.6363636363636</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>3184090.909090909</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>24.5625</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>180.1875</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>681875</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>1607500</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>174</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>344</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>25150000</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>388</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>bg55fwUm</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>45477.91666666666</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flores g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F151" t="n">
+        <v>8023</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>59</v>
+      </c>
+      <c r="L151" t="n">
+        <v>41</v>
+      </c>
+      <c r="M151" t="n">
+        <v>23</v>
+      </c>
+      <c r="N151" t="n">
+        <v>10</v>
+      </c>
+      <c r="O151" t="n">
+        <v>8</v>
+      </c>
+      <c r="P151" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>19</v>
+      </c>
+      <c r="R151" t="n">
+        <v>12</v>
+      </c>
+      <c r="S151" t="n">
+        <v>8</v>
+      </c>
+      <c r="T151" t="n">
+        <v>8</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="W151" t="n">
+        <v>167</v>
+      </c>
+      <c r="X151" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="inlineStr"/>
+      <c r="AP151" t="inlineStr"/>
+      <c r="AQ151" t="inlineStr"/>
+      <c r="AR151" t="inlineStr"/>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AU151" t="inlineStr"/>
+      <c r="AV151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr"/>
+      <c r="AX151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr"/>
+      <c r="BA151" t="inlineStr"/>
+      <c r="BB151" t="inlineStr"/>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
+      <c r="BI151" t="inlineStr"/>
+      <c r="BJ151" t="inlineStr"/>
+      <c r="BK151" t="inlineStr"/>
+      <c r="BL151" t="inlineStr"/>
+      <c r="BM151" t="inlineStr"/>
+      <c r="BN151" t="inlineStr"/>
+      <c r="BO151" t="inlineStr"/>
+      <c r="BP151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>xp49gcqf</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>45478.85416666666</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">montero r 
+  cos </t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beirne stadium
+  pawtucket  ri </t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>5252</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4728</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>61</v>
+      </c>
+      <c r="L152" t="n">
+        <v>39</v>
+      </c>
+      <c r="M152" t="n">
+        <v>13</v>
+      </c>
+      <c r="N152" t="n">
+        <v>11</v>
+      </c>
+      <c r="O152" t="n">
+        <v>6</v>
+      </c>
+      <c r="P152" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>12</v>
+      </c>
+      <c r="R152" t="n">
+        <v>11</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="n">
+        <v>7</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="W152" t="n">
+        <v>167</v>
+      </c>
+      <c r="X152" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr"/>
+      <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr"/>
+      <c r="AO152" t="inlineStr"/>
+      <c r="AP152" t="inlineStr"/>
+      <c r="AQ152" t="inlineStr"/>
+      <c r="AR152" t="inlineStr"/>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AU152" t="inlineStr"/>
+      <c r="AV152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr"/>
+      <c r="AX152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr"/>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
+      <c r="BI152" t="inlineStr"/>
+      <c r="BJ152" t="inlineStr"/>
+      <c r="BK152" t="inlineStr"/>
+      <c r="BL152" t="inlineStr"/>
+      <c r="BM152" t="inlineStr"/>
+      <c r="BN152" t="inlineStr"/>
+      <c r="BO152" t="inlineStr"/>
+      <c r="BP152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>6J8DhHb0</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45478.83333333334</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F153" t="n">
+        <v>3396</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>63</v>
+      </c>
+      <c r="L153" t="n">
+        <v>37</v>
+      </c>
+      <c r="M153" t="n">
+        <v>25</v>
+      </c>
+      <c r="N153" t="n">
+        <v>9</v>
+      </c>
+      <c r="O153" t="n">
+        <v>6</v>
+      </c>
+      <c r="P153" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>14</v>
+      </c>
+      <c r="S153" t="n">
+        <v>8</v>
+      </c>
+      <c r="T153" t="n">
+        <v>4</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="W153" t="n">
+        <v>167</v>
+      </c>
+      <c r="X153" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr"/>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr"/>
+      <c r="AO153" t="inlineStr"/>
+      <c r="AP153" t="inlineStr"/>
+      <c r="AQ153" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>62</v>
+      </c>
+      <c r="AW153" t="inlineStr"/>
+      <c r="AX153" t="inlineStr"/>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr"/>
+      <c r="BA153" t="inlineStr"/>
+      <c r="BB153" t="inlineStr"/>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
+      <c r="BI153" t="inlineStr"/>
+      <c r="BJ153" t="inlineStr"/>
+      <c r="BK153" t="inlineStr"/>
+      <c r="BL153" t="inlineStr"/>
+      <c r="BM153" t="inlineStr"/>
+      <c r="BN153" t="inlineStr"/>
+      <c r="BO153" t="inlineStr"/>
+      <c r="BP153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F154" t="n">
+        <v>30017</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>57</v>
+      </c>
+      <c r="L154" t="n">
+        <v>43</v>
+      </c>
+      <c r="M154" t="n">
+        <v>15</v>
+      </c>
+      <c r="N154" t="n">
+        <v>12</v>
+      </c>
+      <c r="O154" t="n">
+        <v>7</v>
+      </c>
+      <c r="P154" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>5</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7</v>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="W154" t="n">
+        <v>167</v>
+      </c>
+      <c r="X154" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2147000</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>1377500</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>177.85</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>67</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3349750</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>25.94117647058824</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>66.58823529411765</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1267647.058823529</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>70.94117647058823</v>
+      </c>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
+      <c r="BI154" t="inlineStr"/>
+      <c r="BJ154" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>143</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45479.95833333334</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F155" t="n">
+        <v>20738</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>48</v>
+      </c>
+      <c r="L155" t="n">
+        <v>52</v>
+      </c>
+      <c r="M155" t="n">
+        <v>10</v>
+      </c>
+      <c r="N155" t="n">
+        <v>15</v>
+      </c>
+      <c r="O155" t="n">
+        <v>5</v>
+      </c>
+      <c r="P155" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>5</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7</v>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="W155" t="n">
+        <v>167</v>
+      </c>
+      <c r="X155" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>66.44444444444444</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1561111.111111111</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>28.56521739130435</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>182.3913043478261</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>63.43478260869565</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>587826.0869565217</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>65.52173913043478</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>20.95238095238095</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>181.9047619047619</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>61.76190476190476</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>1228571.428571429</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
+      <c r="BI155" t="inlineStr"/>
+      <c r="BJ155" t="inlineStr"/>
+      <c r="BK155" t="inlineStr"/>
+      <c r="BL155" t="inlineStr"/>
+      <c r="BM155" t="inlineStr"/>
+      <c r="BN155" t="inlineStr"/>
+      <c r="BO155" t="inlineStr"/>
+      <c r="BP155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F156" t="n">
+        <v>20396</v>
+      </c>
+      <c r="G156" t="n">
+        <v>5</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>62</v>
+      </c>
+      <c r="L156" t="n">
+        <v>38</v>
+      </c>
+      <c r="M156" t="n">
+        <v>10</v>
+      </c>
+      <c r="N156" t="n">
+        <v>13</v>
+      </c>
+      <c r="O156" t="n">
+        <v>6</v>
+      </c>
+      <c r="P156" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>11</v>
+      </c>
+      <c r="R156" t="n">
+        <v>8</v>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="W156" t="n">
+        <v>167</v>
+      </c>
+      <c r="X156" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2095500</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>999090.9090909091</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>26.69565217391304</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>178.0434782608696</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>65.34782608695652</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>1361304.347826087</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>69.39130434782609</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>927500</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>128</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>131</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>139</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F157" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>57</v>
+      </c>
+      <c r="L157" t="n">
+        <v>43</v>
+      </c>
+      <c r="M157" t="n">
+        <v>15</v>
+      </c>
+      <c r="N157" t="n">
+        <v>13</v>
+      </c>
+      <c r="O157" t="n">
+        <v>3</v>
+      </c>
+      <c r="P157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>6</v>
+      </c>
+      <c r="R157" t="n">
+        <v>5</v>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="W157" t="n">
+        <v>167</v>
+      </c>
+      <c r="X157" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE157" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>181.1818181818182</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1438636.363636364</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2652500</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>177.8333333333333</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>65.375</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>1449583.333333333</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>71.45833333333333</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1416250</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>177</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>206</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>212</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>177</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>266</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F158" t="n">
+        <v>20547</v>
+      </c>
+      <c r="G158" t="n">
+        <v>4</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
+        <v>58</v>
+      </c>
+      <c r="L158" t="n">
+        <v>42</v>
+      </c>
+      <c r="M158" t="n">
+        <v>11</v>
+      </c>
+      <c r="N158" t="n">
+        <v>8</v>
+      </c>
+      <c r="O158" t="n">
+        <v>6</v>
+      </c>
+      <c r="P158" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>8</v>
+      </c>
+      <c r="R158" t="n">
+        <v>16</v>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="W158" t="n">
+        <v>167</v>
+      </c>
+      <c r="X158" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AE158" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>4030000</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1644500</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>180.2272727272727</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>63.72727272727273</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>70.13636363636364</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>24.90476190476191</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>179.8095238095238</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>65.76190476190476</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>3052619.047619048</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>37</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>186</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>117</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>990000</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F159" t="n">
+        <v>25513</v>
+      </c>
+      <c r="G159" t="n">
+        <v>6</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>51</v>
+      </c>
+      <c r="L159" t="n">
+        <v>49</v>
+      </c>
+      <c r="M159" t="n">
+        <v>15</v>
+      </c>
+      <c r="N159" t="n">
+        <v>9</v>
+      </c>
+      <c r="O159" t="n">
+        <v>10</v>
+      </c>
+      <c r="P159" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>13</v>
+      </c>
+      <c r="R159" t="n">
+        <v>14</v>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="W159" t="n">
+        <v>167</v>
+      </c>
+      <c r="X159" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AE159" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>3686363.636363636</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>3652500</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>182.4583333333333</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>61.70833333333334</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>1384166.666666667</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>20.47058823529412</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>184.3529411764706</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>63.88235294117647</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>1686764.705882353</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>75.52941176470588</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>119</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>128</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>369</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>59225000</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F160" t="n">
+        <v>22561</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>56</v>
+      </c>
+      <c r="L160" t="n">
+        <v>44</v>
+      </c>
+      <c r="M160" t="n">
+        <v>24</v>
+      </c>
+      <c r="N160" t="n">
+        <v>5</v>
+      </c>
+      <c r="O160" t="n">
+        <v>10</v>
+      </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>5</v>
+      </c>
+      <c r="R160" t="n">
+        <v>8</v>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="W160" t="n">
+        <v>167</v>
+      </c>
+      <c r="X160" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2372500</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1315000</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>25.43478260869565</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>180.4782608695652</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>67.43478260869566</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>3493913.043478261</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>73</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>21.58333333333333</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>494583.3333333333</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>67.16666666666667</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>106</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>615000</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>143</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>248</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>52</v>
+      </c>
+      <c r="L161" t="n">
+        <v>48</v>
+      </c>
+      <c r="M161" t="n">
+        <v>15</v>
+      </c>
+      <c r="N161" t="n">
+        <v>15</v>
+      </c>
+      <c r="O161" t="n">
+        <v>5</v>
+      </c>
+      <c r="P161" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>8</v>
+      </c>
+      <c r="R161" t="n">
+        <v>10</v>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="W161" t="n">
+        <v>167</v>
+      </c>
+      <c r="X161" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>184.2222222222222</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>70.11111111111111</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>3138888.888888889</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>66</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>2322000</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>25.64285714285714</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>181.6428571428571</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>65</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>1043571.428571429</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>70.35714285714286</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>22.88235294117647</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>182.7058823529412</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>63.70588235294117</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>1177647.058823529</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>345</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>13075000</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>358</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>249</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>hCl8EbLJ</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>45479.95833333334</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radosav c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laney college football stadium
+  oakland  ca </t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2631</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>50</v>
+      </c>
+      <c r="L162" t="n">
+        <v>50</v>
+      </c>
+      <c r="M162" t="n">
+        <v>8</v>
+      </c>
+      <c r="N162" t="n">
+        <v>8</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2</v>
+      </c>
+      <c r="P162" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>10</v>
+      </c>
+      <c r="R162" t="n">
+        <v>14</v>
+      </c>
+      <c r="S162" t="n">
+        <v>12</v>
+      </c>
+      <c r="T162" t="n">
+        <v>7</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="W162" t="n">
+        <v>167</v>
+      </c>
+      <c r="X162" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="inlineStr"/>
+      <c r="AK162" t="inlineStr"/>
+      <c r="AL162" t="inlineStr"/>
+      <c r="AM162" t="inlineStr"/>
+      <c r="AN162" t="inlineStr"/>
+      <c r="AO162" t="inlineStr"/>
+      <c r="AP162" t="inlineStr"/>
+      <c r="AQ162" t="inlineStr"/>
+      <c r="AR162" t="inlineStr"/>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AU162" t="inlineStr"/>
+      <c r="AV162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr"/>
+      <c r="AX162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr"/>
+      <c r="BA162" t="inlineStr"/>
+      <c r="BB162" t="inlineStr"/>
+      <c r="BC162" t="inlineStr"/>
+      <c r="BD162" t="inlineStr"/>
+      <c r="BE162" t="inlineStr"/>
+      <c r="BF162" t="inlineStr"/>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
+      <c r="BI162" t="inlineStr"/>
+      <c r="BJ162" t="inlineStr"/>
+      <c r="BK162" t="inlineStr"/>
+      <c r="BL162" t="inlineStr"/>
+      <c r="BM162" t="inlineStr"/>
+      <c r="BN162" t="inlineStr"/>
+      <c r="BO162" t="inlineStr"/>
+      <c r="BP162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>W2mCDIzQ</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>45479.95833333334</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F163" t="n">
+        <v>3725</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>40</v>
+      </c>
+      <c r="L163" t="n">
+        <v>60</v>
+      </c>
+      <c r="M163" t="n">
+        <v>13</v>
+      </c>
+      <c r="N163" t="n">
+        <v>15</v>
+      </c>
+      <c r="O163" t="n">
+        <v>8</v>
+      </c>
+      <c r="P163" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>7</v>
+      </c>
+      <c r="R163" t="n">
+        <v>15</v>
+      </c>
+      <c r="S163" t="n">
+        <v>11</v>
+      </c>
+      <c r="T163" t="n">
+        <v>6</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="W163" t="n">
+        <v>167</v>
+      </c>
+      <c r="X163" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="inlineStr"/>
+      <c r="AK163" t="inlineStr"/>
+      <c r="AL163" t="inlineStr"/>
+      <c r="AM163" t="inlineStr"/>
+      <c r="AN163" t="inlineStr"/>
+      <c r="AO163" t="inlineStr"/>
+      <c r="AP163" t="inlineStr"/>
+      <c r="AQ163" t="inlineStr"/>
+      <c r="AR163" t="inlineStr"/>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AU163" t="inlineStr"/>
+      <c r="AV163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr"/>
+      <c r="AX163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr"/>
+      <c r="BA163" t="inlineStr"/>
+      <c r="BB163" t="inlineStr"/>
+      <c r="BC163" t="inlineStr"/>
+      <c r="BD163" t="inlineStr"/>
+      <c r="BE163" t="inlineStr"/>
+      <c r="BF163" t="inlineStr"/>
+      <c r="BG163" t="inlineStr"/>
+      <c r="BH163" t="inlineStr"/>
+      <c r="BI163" t="inlineStr"/>
+      <c r="BJ163" t="inlineStr"/>
+      <c r="BK163" t="inlineStr"/>
+      <c r="BL163" t="inlineStr"/>
+      <c r="BM163" t="inlineStr"/>
+      <c r="BN163" t="inlineStr"/>
+      <c r="BO163" t="inlineStr"/>
+      <c r="BP163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>jmUr8dbm</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>45479.95138888889</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dopka g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota field
+  san antonio  tx </t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F164" t="n">
+        <v>6011</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>42</v>
+      </c>
+      <c r="L164" t="n">
+        <v>58</v>
+      </c>
+      <c r="M164" t="n">
+        <v>8</v>
+      </c>
+      <c r="N164" t="n">
+        <v>12</v>
+      </c>
+      <c r="O164" t="n">
+        <v>4</v>
+      </c>
+      <c r="P164" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>21</v>
+      </c>
+      <c r="R164" t="n">
+        <v>8</v>
+      </c>
+      <c r="S164" t="n">
+        <v>4</v>
+      </c>
+      <c r="T164" t="n">
+        <v>6</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="W164" t="n">
+        <v>167</v>
+      </c>
+      <c r="X164" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="inlineStr"/>
+      <c r="AK164" t="inlineStr"/>
+      <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
+      <c r="AN164" t="inlineStr"/>
+      <c r="AO164" t="inlineStr"/>
+      <c r="AP164" t="inlineStr"/>
+      <c r="AQ164" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>314285.7142857143</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>65.14285714285714</v>
+      </c>
+      <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr"/>
+      <c r="BA164" t="inlineStr"/>
+      <c r="BB164" t="inlineStr"/>
+      <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr"/>
+      <c r="BH164" t="inlineStr"/>
+      <c r="BI164" t="inlineStr"/>
+      <c r="BJ164" t="inlineStr"/>
+      <c r="BK164" t="inlineStr"/>
+      <c r="BL164" t="inlineStr"/>
+      <c r="BM164" t="inlineStr"/>
+      <c r="BN164" t="inlineStr"/>
+      <c r="BO164" t="inlineStr"/>
+      <c r="BP164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>v90QkFrJ</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45479.875</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wakemed soccer park
+  cary  nc </t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2161</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>49</v>
+      </c>
+      <c r="L165" t="n">
+        <v>51</v>
+      </c>
+      <c r="M165" t="n">
+        <v>18</v>
+      </c>
+      <c r="N165" t="n">
+        <v>14</v>
+      </c>
+      <c r="O165" t="n">
+        <v>7</v>
+      </c>
+      <c r="P165" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>11</v>
+      </c>
+      <c r="R165" t="n">
+        <v>13</v>
+      </c>
+      <c r="S165" t="n">
+        <v>6</v>
+      </c>
+      <c r="T165" t="n">
+        <v>3</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="W165" t="n">
+        <v>167</v>
+      </c>
+      <c r="X165" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr"/>
+      <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
+      <c r="AN165" t="inlineStr"/>
+      <c r="AO165" t="inlineStr"/>
+      <c r="AP165" t="inlineStr"/>
+      <c r="AQ165" t="inlineStr"/>
+      <c r="AR165" t="inlineStr"/>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AU165" t="inlineStr"/>
+      <c r="AV165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr"/>
+      <c r="AX165" t="inlineStr"/>
+      <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr"/>
+      <c r="BA165" t="inlineStr"/>
+      <c r="BB165" t="inlineStr"/>
+      <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr"/>
+      <c r="BH165" t="inlineStr"/>
+      <c r="BI165" t="inlineStr"/>
+      <c r="BJ165" t="inlineStr"/>
+      <c r="BK165" t="inlineStr"/>
+      <c r="BL165" t="inlineStr"/>
+      <c r="BM165" t="inlineStr"/>
+      <c r="BN165" t="inlineStr"/>
+      <c r="BO165" t="inlineStr"/>
+      <c r="BP165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pA7HiyE6</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>45479.83333333334</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hassan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyworth stadium
+  hamtramck  mi </t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>7933</v>
+      </c>
+      <c r="F166" t="n">
+        <v>6403</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>50</v>
+      </c>
+      <c r="L166" t="n">
+        <v>50</v>
+      </c>
+      <c r="M166" t="n">
+        <v>4</v>
+      </c>
+      <c r="N166" t="n">
+        <v>20</v>
+      </c>
+      <c r="O166" t="n">
+        <v>2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>16</v>
+      </c>
+      <c r="R166" t="n">
+        <v>26</v>
+      </c>
+      <c r="S166" t="n">
+        <v>4</v>
+      </c>
+      <c r="T166" t="n">
+        <v>6</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="W166" t="n">
+        <v>167</v>
+      </c>
+      <c r="X166" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr"/>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr"/>
+      <c r="AO166" t="inlineStr"/>
+      <c r="AP166" t="inlineStr"/>
+      <c r="AQ166" t="inlineStr"/>
+      <c r="AR166" t="inlineStr"/>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AU166" t="inlineStr"/>
+      <c r="AV166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr"/>
+      <c r="AX166" t="inlineStr"/>
+      <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr"/>
+      <c r="BA166" t="inlineStr"/>
+      <c r="BB166" t="inlineStr"/>
+      <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr"/>
+      <c r="BH166" t="inlineStr"/>
+      <c r="BI166" t="inlineStr"/>
+      <c r="BJ166" t="inlineStr"/>
+      <c r="BK166" t="inlineStr"/>
+      <c r="BL166" t="inlineStr"/>
+      <c r="BM166" t="inlineStr"/>
+      <c r="BN166" t="inlineStr"/>
+      <c r="BO166" t="inlineStr"/>
+      <c r="BP166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>CdVv9xqs</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>45479.83333333334</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">surgan j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F167" t="n">
+        <v>5018</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>53</v>
+      </c>
+      <c r="L167" t="n">
+        <v>47</v>
+      </c>
+      <c r="M167" t="n">
+        <v>17</v>
+      </c>
+      <c r="N167" t="n">
+        <v>5</v>
+      </c>
+      <c r="O167" t="n">
+        <v>8</v>
+      </c>
+      <c r="P167" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>6</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="n">
+        <v>5</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="W167" t="n">
+        <v>167</v>
+      </c>
+      <c r="X167" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr"/>
+      <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
+      <c r="AN167" t="inlineStr"/>
+      <c r="AO167" t="inlineStr"/>
+      <c r="AP167" t="inlineStr"/>
+      <c r="AQ167" t="inlineStr"/>
+      <c r="AR167" t="inlineStr"/>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AU167" t="inlineStr"/>
+      <c r="AV167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr"/>
+      <c r="AX167" t="inlineStr"/>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr"/>
+      <c r="BA167" t="inlineStr"/>
+      <c r="BB167" t="inlineStr"/>
+      <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr"/>
+      <c r="BH167" t="inlineStr"/>
+      <c r="BI167" t="inlineStr"/>
+      <c r="BJ167" t="inlineStr"/>
+      <c r="BK167" t="inlineStr"/>
+      <c r="BL167" t="inlineStr"/>
+      <c r="BM167" t="inlineStr"/>
+      <c r="BN167" t="inlineStr"/>
+      <c r="BO167" t="inlineStr"/>
+      <c r="BP167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F168" t="n">
+        <v>19302</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>57</v>
+      </c>
+      <c r="L168" t="n">
+        <v>43</v>
+      </c>
+      <c r="M168" t="n">
+        <v>14</v>
+      </c>
+      <c r="N168" t="n">
+        <v>16</v>
+      </c>
+      <c r="O168" t="n">
+        <v>4</v>
+      </c>
+      <c r="P168" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>4</v>
+      </c>
+      <c r="R168" t="n">
+        <v>13</v>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="W168" t="n">
+        <v>167</v>
+      </c>
+      <c r="X168" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE168" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>178</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>3965000</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>22.73684210526316</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>180.1578947368421</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>65.10526315789474</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>2197368.421052631</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>25.52631578947368</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>177.4736842105263</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>65.21052631578948</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>1424736.842105263</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>70.10526315789474</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>184</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F169" t="n">
+        <v>20616</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>52</v>
+      </c>
+      <c r="L169" t="n">
+        <v>48</v>
+      </c>
+      <c r="M169" t="n">
+        <v>16</v>
+      </c>
+      <c r="N169" t="n">
+        <v>12</v>
+      </c>
+      <c r="O169" t="n">
+        <v>8</v>
+      </c>
+      <c r="P169" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>10</v>
+      </c>
+      <c r="R169" t="n">
+        <v>11</v>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>CfE5JcGF</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="W169" t="n">
+        <v>167</v>
+      </c>
+      <c r="X169" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE169" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>177.0909090909091</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2229545.454545455</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>3270909.090909091</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>182.85</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>1394000</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>28.1304347826087</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>184.0869565217391</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>1.08695652173913</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>65.26086956521739</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1756739.130434783</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>66.39130434782609</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>285</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>14275000</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>288</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>321</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F170" t="n">
+        <v>16331</v>
+      </c>
+      <c r="G170" t="n">
+        <v>4</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>53</v>
+      </c>
+      <c r="L170" t="n">
+        <v>47</v>
+      </c>
+      <c r="M170" t="n">
+        <v>16</v>
+      </c>
+      <c r="N170" t="n">
+        <v>15</v>
+      </c>
+      <c r="O170" t="n">
+        <v>7</v>
+      </c>
+      <c r="P170" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>6</v>
+      </c>
+      <c r="R170" t="n">
+        <v>12</v>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="W170" t="n">
+        <v>167</v>
+      </c>
+      <c r="X170" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE170" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1256000</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>524000</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>24.82352941176471</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>184.2352941176471</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>62.94117647058823</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>913235.2941176471</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>68.11764705882354</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>141</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>154</v>
+      </c>
+      <c r="BJ170" t="inlineStr"/>
+      <c r="BK170" t="inlineStr"/>
+      <c r="BL170" t="inlineStr"/>
+      <c r="BM170" t="inlineStr"/>
+      <c r="BN170" t="inlineStr"/>
+      <c r="BO170" t="inlineStr"/>
+      <c r="BP170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>46</v>
+      </c>
+      <c r="L171" t="n">
+        <v>54</v>
+      </c>
+      <c r="M171" t="n">
+        <v>12</v>
+      </c>
+      <c r="N171" t="n">
+        <v>10</v>
+      </c>
+      <c r="O171" t="n">
+        <v>4</v>
+      </c>
+      <c r="P171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>7</v>
+      </c>
+      <c r="R171" t="n">
+        <v>11</v>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="W171" t="n">
+        <v>167</v>
+      </c>
+      <c r="X171" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AE171" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2512000</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>2381818.181818182</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>67.125</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>1723958.333333333</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>69.45833333333333</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>181.4375</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>63.625</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>859062.5</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>68</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>134</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>407</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>10475000</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F172" t="n">
+        <v>17457</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>54</v>
+      </c>
+      <c r="L172" t="n">
+        <v>46</v>
+      </c>
+      <c r="M172" t="n">
+        <v>18</v>
+      </c>
+      <c r="N172" t="n">
+        <v>12</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7</v>
+      </c>
+      <c r="P172" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>18</v>
+      </c>
+      <c r="R172" t="n">
+        <v>9</v>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="W172" t="n">
+        <v>167</v>
+      </c>
+      <c r="X172" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE172" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>64.09090909090909</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1050909.090909091</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>61.88888888888889</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>756666.6666666666</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>68.88888888888889</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>64.625</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>1101875</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>68.04166666666667</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>27.31818181818182</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>2889090.909090909</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>70.22727272727273</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>208</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>409</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>25650000</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>51</v>
+      </c>
+      <c r="L173" t="n">
+        <v>49</v>
+      </c>
+      <c r="M173" t="n">
+        <v>22</v>
+      </c>
+      <c r="N173" t="n">
+        <v>10</v>
+      </c>
+      <c r="O173" t="n">
+        <v>9</v>
+      </c>
+      <c r="P173" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>10</v>
+      </c>
+      <c r="R173" t="n">
+        <v>15</v>
+      </c>
+      <c r="S173" t="n">
+        <v>7</v>
+      </c>
+      <c r="T173" t="n">
+        <v>9</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="W173" t="n">
+        <v>167</v>
+      </c>
+      <c r="X173" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>3767500</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AK173" t="inlineStr"/>
+      <c r="AL173" t="inlineStr"/>
+      <c r="AM173" t="inlineStr"/>
+      <c r="AN173" t="inlineStr"/>
+      <c r="AO173" t="inlineStr"/>
+      <c r="AP173" t="inlineStr"/>
+      <c r="AQ173" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>177.9090909090909</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>66.77272727272727</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>1992045.454545455</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>73.22727272727273</v>
+      </c>
+      <c r="AW173" t="inlineStr"/>
+      <c r="AX173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr"/>
+      <c r="BA173" t="inlineStr"/>
+      <c r="BB173" t="inlineStr"/>
+      <c r="BC173" t="inlineStr"/>
+      <c r="BD173" t="inlineStr"/>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr"/>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
+      <c r="BI173" t="inlineStr"/>
+      <c r="BJ173" t="inlineStr"/>
+      <c r="BK173" t="inlineStr"/>
+      <c r="BL173" t="inlineStr"/>
+      <c r="BM173" t="inlineStr"/>
+      <c r="BN173" t="inlineStr"/>
+      <c r="BO173" t="inlineStr"/>
+      <c r="BP173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>51</v>
+      </c>
+      <c r="L174" t="n">
+        <v>49</v>
+      </c>
+      <c r="M174" t="n">
+        <v>14</v>
+      </c>
+      <c r="N174" t="n">
+        <v>16</v>
+      </c>
+      <c r="O174" t="n">
+        <v>7</v>
+      </c>
+      <c r="P174" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>15</v>
+      </c>
+      <c r="R174" t="n">
+        <v>17</v>
+      </c>
+      <c r="S174" t="n">
+        <v>9</v>
+      </c>
+      <c r="T174" t="n">
+        <v>9</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="W174" t="n">
+        <v>167</v>
+      </c>
+      <c r="X174" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE174" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1366500</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>2377272.727272727</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>26.68421052631579</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>179.9473684210526</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>65.47368421052632</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>67.78947368421052</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>181.2666666666667</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>59.93333333333333</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>391000</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>63.73333333333333</v>
+      </c>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
+      <c r="BI174" t="inlineStr"/>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="inlineStr"/>
+      <c r="BL174" t="inlineStr"/>
+      <c r="BM174" t="inlineStr"/>
+      <c r="BN174" t="inlineStr"/>
+      <c r="BO174" t="inlineStr"/>
+      <c r="BP174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>49</v>
+      </c>
+      <c r="L175" t="n">
+        <v>51</v>
+      </c>
+      <c r="M175" t="n">
+        <v>11</v>
+      </c>
+      <c r="N175" t="n">
+        <v>9</v>
+      </c>
+      <c r="O175" t="n">
+        <v>2</v>
+      </c>
+      <c r="P175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>22</v>
+      </c>
+      <c r="R175" t="n">
+        <v>13</v>
+      </c>
+      <c r="S175" t="n">
+        <v>9</v>
+      </c>
+      <c r="T175" t="n">
+        <v>17</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="W175" t="n">
+        <v>167</v>
+      </c>
+      <c r="X175" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>2017000</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AQ175" t="inlineStr"/>
+      <c r="AR175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>66.5625</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>2464687.5</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>72.6875</v>
+      </c>
+      <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
+      <c r="BM175" t="inlineStr"/>
+      <c r="BN175" t="inlineStr"/>
+      <c r="BO175" t="inlineStr"/>
+      <c r="BP175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fifth third bank stadium
+  kennesaw  ga </t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>8318</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>70</v>
+      </c>
+      <c r="L176" t="n">
+        <v>30</v>
+      </c>
+      <c r="M176" t="n">
+        <v>17</v>
+      </c>
+      <c r="N176" t="n">
+        <v>8</v>
+      </c>
+      <c r="O176" t="n">
+        <v>3</v>
+      </c>
+      <c r="P176" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>20</v>
+      </c>
+      <c r="R176" t="n">
+        <v>18</v>
+      </c>
+      <c r="S176" t="n">
+        <v>7</v>
+      </c>
+      <c r="T176" t="n">
+        <v>7</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="W176" t="n">
+        <v>167</v>
+      </c>
+      <c r="X176" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1235000</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AK176" t="inlineStr"/>
+      <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
+      <c r="AN176" t="inlineStr"/>
+      <c r="AO176" t="inlineStr"/>
+      <c r="AP176" t="inlineStr"/>
+      <c r="AQ176" t="n">
+        <v>25.15789473684211</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>180.2631578947368</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>64.10526315789474</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>834210.5263157894</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>71.21052631578948</v>
+      </c>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
+      <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr"/>
+      <c r="BA176" t="inlineStr"/>
+      <c r="BB176" t="inlineStr"/>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
+      <c r="BH176" t="inlineStr"/>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
+      <c r="BO176" t="inlineStr"/>
+      <c r="BP176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>pATn7GDg</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>45485.91666666666</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">berna rico s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">southwest university park
+  el paso  tx </t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F177" t="n">
+        <v>6727</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>37</v>
+      </c>
+      <c r="L177" t="n">
+        <v>63</v>
+      </c>
+      <c r="M177" t="n">
+        <v>7</v>
+      </c>
+      <c r="N177" t="n">
+        <v>10</v>
+      </c>
+      <c r="O177" t="n">
+        <v>3</v>
+      </c>
+      <c r="P177" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>7</v>
+      </c>
+      <c r="R177" t="n">
+        <v>7</v>
+      </c>
+      <c r="S177" t="n">
+        <v>6</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="W177" t="n">
+        <v>167</v>
+      </c>
+      <c r="X177" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
+      <c r="AJ177" t="inlineStr"/>
+      <c r="AK177" t="inlineStr"/>
+      <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
+      <c r="AN177" t="inlineStr"/>
+      <c r="AO177" t="inlineStr"/>
+      <c r="AP177" t="inlineStr"/>
+      <c r="AQ177" t="inlineStr"/>
+      <c r="AR177" t="inlineStr"/>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AU177" t="inlineStr"/>
+      <c r="AV177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr"/>
+      <c r="BA177" t="inlineStr"/>
+      <c r="BB177" t="inlineStr"/>
+      <c r="BC177" t="inlineStr"/>
+      <c r="BD177" t="inlineStr"/>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
+      <c r="BO177" t="inlineStr"/>
+      <c r="BP177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>bDXj6zTa</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>45485.85416666666</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trinity health stadium
+  east hartford  ct </t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4809</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>39</v>
+      </c>
+      <c r="L178" t="n">
+        <v>61</v>
+      </c>
+      <c r="M178" t="n">
+        <v>10</v>
+      </c>
+      <c r="N178" t="n">
+        <v>24</v>
+      </c>
+      <c r="O178" t="n">
+        <v>2</v>
+      </c>
+      <c r="P178" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>15</v>
+      </c>
+      <c r="R178" t="n">
+        <v>16</v>
+      </c>
+      <c r="S178" t="n">
+        <v>6</v>
+      </c>
+      <c r="T178" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="W178" t="n">
+        <v>167</v>
+      </c>
+      <c r="X178" t="n">
+        <v>1673</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
+      <c r="AJ178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr"/>
+      <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr"/>
+      <c r="AP178" t="inlineStr"/>
+      <c r="AQ178" t="inlineStr"/>
+      <c r="AR178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AU178" t="inlineStr"/>
+      <c r="AV178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr"/>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
+      <c r="BO178" t="inlineStr"/>
+      <c r="BP178" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36863,6 +36863,3132 @@
       <c r="BO200" t="inlineStr"/>
       <c r="BP200" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>08pcD25G</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>45490.98958333334</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez g  jr 
+  usa </t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F201" t="n">
+        <v>22163</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>44</v>
+      </c>
+      <c r="L201" t="n">
+        <v>56</v>
+      </c>
+      <c r="M201" t="n">
+        <v>8</v>
+      </c>
+      <c r="N201" t="n">
+        <v>20</v>
+      </c>
+      <c r="O201" t="n">
+        <v>5</v>
+      </c>
+      <c r="P201" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>12</v>
+      </c>
+      <c r="R201" t="n">
+        <v>19</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="U201" t="n">
+        <v>167</v>
+      </c>
+      <c r="V201" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AE201" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>4560000</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>1592500</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>25.35294117647059</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>181.1176470588235</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>66.70588235294117</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>1464705.882352941</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>73.82352941176471</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>855000</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>199</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>209</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>280</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>KdTaErjA</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>45490.97916666666</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F202" t="n">
+        <v>19488</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>54</v>
+      </c>
+      <c r="L202" t="n">
+        <v>46</v>
+      </c>
+      <c r="M202" t="n">
+        <v>16</v>
+      </c>
+      <c r="N202" t="n">
+        <v>9</v>
+      </c>
+      <c r="O202" t="n">
+        <v>9</v>
+      </c>
+      <c r="P202" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>11</v>
+      </c>
+      <c r="R202" t="n">
+        <v>8</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="U202" t="n">
+        <v>167</v>
+      </c>
+      <c r="V202" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W202" t="n">
+        <v>0</v>
+      </c>
+      <c r="X202" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AE202" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>3882500</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>181.1111111111111</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>64.77777777777777</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1307777.777777778</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>26.05555555555556</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>180.6111111111111</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>64.05555555555556</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>1022222.222222222</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>68.05555555555556</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>22.39130434782609</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>59.52173913043478</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>609565.2173913043</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>67.82608695652173</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>183</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>67</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>vaq1CMKM</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>45490.97916666666</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F203" t="n">
+        <v>12177</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>44</v>
+      </c>
+      <c r="L203" t="n">
+        <v>56</v>
+      </c>
+      <c r="M203" t="n">
+        <v>10</v>
+      </c>
+      <c r="N203" t="n">
+        <v>25</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>18</v>
+      </c>
+      <c r="R203" t="n">
+        <v>15</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="U203" t="n">
+        <v>167</v>
+      </c>
+      <c r="V203" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W203" t="n">
+        <v>0</v>
+      </c>
+      <c r="X203" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AE203" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>2665000</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>2095909.090909091</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>72</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>180.48</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>1257800</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>25.73913043478261</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>178.6521739130435</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>64.95652173913044</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>991521.7391304348</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>67.65217391304348</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>134</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>175</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>62</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>YLr5BtzT</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>45490.97916666666</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F204" t="n">
+        <v>30032</v>
+      </c>
+      <c r="G204" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>66</v>
+      </c>
+      <c r="L204" t="n">
+        <v>34</v>
+      </c>
+      <c r="M204" t="n">
+        <v>6</v>
+      </c>
+      <c r="N204" t="n">
+        <v>12</v>
+      </c>
+      <c r="O204" t="n">
+        <v>2</v>
+      </c>
+      <c r="P204" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>9</v>
+      </c>
+      <c r="R204" t="n">
+        <v>15</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="U204" t="n">
+        <v>167</v>
+      </c>
+      <c r="V204" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W204" t="n">
+        <v>0</v>
+      </c>
+      <c r="X204" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE204" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1696250</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>2105000</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>25.20833333333333</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>177.625</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>67.70833333333333</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>2492708.333333333</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>23.19047619047619</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>62.04761904761905</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>1108333.333333333</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>69.76190476190476</v>
+      </c>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="inlineStr"/>
+      <c r="BL204" t="inlineStr"/>
+      <c r="BM204" t="inlineStr"/>
+      <c r="BN204" t="inlineStr"/>
+      <c r="BO204" t="inlineStr"/>
+      <c r="BP204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>rRYfhY72</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>45490.97916666666</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F205" t="n">
+        <v>23198</v>
+      </c>
+      <c r="G205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>56</v>
+      </c>
+      <c r="L205" t="n">
+        <v>44</v>
+      </c>
+      <c r="M205" t="n">
+        <v>14</v>
+      </c>
+      <c r="N205" t="n">
+        <v>18</v>
+      </c>
+      <c r="O205" t="n">
+        <v>4</v>
+      </c>
+      <c r="P205" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>10</v>
+      </c>
+      <c r="R205" t="n">
+        <v>8</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="U205" t="n">
+        <v>167</v>
+      </c>
+      <c r="V205" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W205" t="n">
+        <v>0</v>
+      </c>
+      <c r="X205" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE205" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2850000</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>181.5454545454545</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>63.81818181818182</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1132727.272727273</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>68.09090909090909</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>25.26086956521739</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>177.1739130434783</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>64.52173913043478</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>1217391.304347826</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>26.26666666666667</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>890333.3333333334</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>70</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>129</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>YuRmHp6i</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>45490.89583333334</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>3</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>41</v>
+      </c>
+      <c r="L206" t="n">
+        <v>59</v>
+      </c>
+      <c r="M206" t="n">
+        <v>9</v>
+      </c>
+      <c r="N206" t="n">
+        <v>12</v>
+      </c>
+      <c r="O206" t="n">
+        <v>6</v>
+      </c>
+      <c r="P206" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>18</v>
+      </c>
+      <c r="R206" t="n">
+        <v>13</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="U206" t="n">
+        <v>167</v>
+      </c>
+      <c r="V206" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W206" t="n">
+        <v>0</v>
+      </c>
+      <c r="X206" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE206" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1965000</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>67</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>2347500</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>26.47368421052632</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>182.6842105263158</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>63.31578947368421</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>1072631.578947368</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>67.31578947368421</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>28.45454545454545</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>180.9545454545455</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>65.72727272727273</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>931136.3636363636</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>67.59090909090909</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>174</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>344</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>25150000</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>388</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>64</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>500000</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>nqViG4Lc</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>45490.89583333334</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F207" t="n">
+        <v>19742</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>3</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>46</v>
+      </c>
+      <c r="L207" t="n">
+        <v>54</v>
+      </c>
+      <c r="M207" t="n">
+        <v>6</v>
+      </c>
+      <c r="N207" t="n">
+        <v>5</v>
+      </c>
+      <c r="O207" t="n">
+        <v>3</v>
+      </c>
+      <c r="P207" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>23</v>
+      </c>
+      <c r="R207" t="n">
+        <v>15</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="U207" t="n">
+        <v>167</v>
+      </c>
+      <c r="V207" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W207" t="n">
+        <v>0</v>
+      </c>
+      <c r="X207" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>64.27272727272727</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1171818.181818182</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>69.81818181818181</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1357500</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>176.875</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>65.5625</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>1518750</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>22.10526315789474</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>184.2105263157895</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>61.94736842105263</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>1055263.157894737</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>71.31578947368421</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>184</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>191</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>182</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>192</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>t6UeFOz4</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>45490.89583333334</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F208" t="n">
+        <v>29070</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>3</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>52</v>
+      </c>
+      <c r="L208" t="n">
+        <v>48</v>
+      </c>
+      <c r="M208" t="n">
+        <v>8</v>
+      </c>
+      <c r="N208" t="n">
+        <v>8</v>
+      </c>
+      <c r="O208" t="n">
+        <v>2</v>
+      </c>
+      <c r="P208" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>12</v>
+      </c>
+      <c r="R208" t="n">
+        <v>11</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="U208" t="n">
+        <v>167</v>
+      </c>
+      <c r="V208" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W208" t="n">
+        <v>0</v>
+      </c>
+      <c r="X208" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE208" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>67.72727272727273</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>2820454.545454545</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>2532500</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>873250</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>26.56521739130435</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>179.8695652173913</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>3205652.173913043</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>70.82608695652173</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>255</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>268</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>185</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>58</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>475000</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>noMTBkUB</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F209" t="n">
+        <v>42524</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>40</v>
+      </c>
+      <c r="L209" t="n">
+        <v>60</v>
+      </c>
+      <c r="M209" t="n">
+        <v>12</v>
+      </c>
+      <c r="N209" t="n">
+        <v>10</v>
+      </c>
+      <c r="O209" t="n">
+        <v>10</v>
+      </c>
+      <c r="P209" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>15</v>
+      </c>
+      <c r="R209" t="n">
+        <v>8</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="U209" t="n">
+        <v>167</v>
+      </c>
+      <c r="V209" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="n">
+        <v>28.45454545454545</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>178</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1124090.909090909</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>21.77777777777778</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>63.66666666666666</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>1380555.555555556</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>180.0625</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>62.625</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>739062.5</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>69.1875</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>181.8461538461538</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>60.69230769230769</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>2115769.230769231</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>73.76923076923077</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>261</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>305</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>181</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>313</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>5995000</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>hpl1gsEp</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F210" t="n">
+        <v>20793</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>71</v>
+      </c>
+      <c r="L210" t="n">
+        <v>29</v>
+      </c>
+      <c r="M210" t="n">
+        <v>26</v>
+      </c>
+      <c r="N210" t="n">
+        <v>13</v>
+      </c>
+      <c r="O210" t="n">
+        <v>9</v>
+      </c>
+      <c r="P210" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>2</v>
+      </c>
+      <c r="R210" t="n">
+        <v>5</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
+        <v>167</v>
+      </c>
+      <c r="V210" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0</v>
+      </c>
+      <c r="X210" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE210" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>181</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>3663636.363636364</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1893181.818181818</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>23.46153846153846</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>180.6923076923077</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>63.23076923076923</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>921538.4615384615</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>70.76923076923077</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>24.47058823529412</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>183.7647058823529</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>63.11764705882353</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>1091764.705882353</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>68.52941176470588</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>123</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>133</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>34</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>QyLXA9qI</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F211" t="n">
+        <v>25513</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>65</v>
+      </c>
+      <c r="L211" t="n">
+        <v>35</v>
+      </c>
+      <c r="M211" t="n">
+        <v>20</v>
+      </c>
+      <c r="N211" t="n">
+        <v>17</v>
+      </c>
+      <c r="O211" t="n">
+        <v>10</v>
+      </c>
+      <c r="P211" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>9</v>
+      </c>
+      <c r="R211" t="n">
+        <v>19</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="U211" t="n">
+        <v>167</v>
+      </c>
+      <c r="V211" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AE211" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1947272.727272727</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>70.72727272727273</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>2097727.272727273</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>24.08333333333333</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>183.0416666666667</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>62.83333333333334</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>1754583.333333333</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>24.78260869565218</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>181.2173913043478</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>65.65217391304348</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>1732391.304347826</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>70.69565217391305</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>335</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>21180000</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>347</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>337</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>8875000</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>Uoi8UUFe</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F212" t="n">
+        <v>20120</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>49</v>
+      </c>
+      <c r="L212" t="n">
+        <v>51</v>
+      </c>
+      <c r="M212" t="n">
+        <v>5</v>
+      </c>
+      <c r="N212" t="n">
+        <v>6</v>
+      </c>
+      <c r="O212" t="n">
+        <v>3</v>
+      </c>
+      <c r="P212" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>18</v>
+      </c>
+      <c r="R212" t="n">
+        <v>13</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="U212" t="n">
+        <v>167</v>
+      </c>
+      <c r="V212" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AE212" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>3812500</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>3539500</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>3641250</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>24.20833333333333</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>180.0416666666667</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>1785625</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>68.95833333333333</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>456</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>72625000</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>474</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>117</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>990000</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>tMfCTlV1</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F213" t="n">
+        <v>15128</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>43</v>
+      </c>
+      <c r="L213" t="n">
+        <v>57</v>
+      </c>
+      <c r="M213" t="n">
+        <v>15</v>
+      </c>
+      <c r="N213" t="n">
+        <v>6</v>
+      </c>
+      <c r="O213" t="n">
+        <v>8</v>
+      </c>
+      <c r="P213" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>10</v>
+      </c>
+      <c r="R213" t="n">
+        <v>11</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
+        <v>167</v>
+      </c>
+      <c r="V213" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W213" t="n">
+        <v>0</v>
+      </c>
+      <c r="X213" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AE213" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1962000</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>66.45454545454545</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>1379545.454545455</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>22.0625</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>182.0625</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>62.4375</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>1271250</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>72.5625</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>24.58333333333333</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>180.1666666666667</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>66.54166666666667</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>1595833.333333333</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>249</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>289</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>187</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>124</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>Wzm5h1Tj</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>45490.85416666666</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F214" t="n">
+        <v>18554</v>
+      </c>
+      <c r="G214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>49</v>
+      </c>
+      <c r="L214" t="n">
+        <v>51</v>
+      </c>
+      <c r="M214" t="n">
+        <v>15</v>
+      </c>
+      <c r="N214" t="n">
+        <v>4</v>
+      </c>
+      <c r="O214" t="n">
+        <v>7</v>
+      </c>
+      <c r="P214" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>10</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="U214" t="n">
+        <v>167</v>
+      </c>
+      <c r="V214" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W214" t="n">
+        <v>0</v>
+      </c>
+      <c r="X214" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>183</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>3409090.909090909</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>73.63636363636364</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>840000</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>24.41666666666667</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>181.5833333333333</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>1118333.333333333</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>24.82352941176471</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>182.3529411764706</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>65.35294117647059</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>1170588.235294118</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>71.58823529411765</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>275000</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>143</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>M9cUJgca</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>45490.875</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">meyer b 
+  usa </t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="n">
+        <v>3</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>54</v>
+      </c>
+      <c r="L215" t="n">
+        <v>46</v>
+      </c>
+      <c r="M215" t="n">
+        <v>12</v>
+      </c>
+      <c r="N215" t="n">
+        <v>13</v>
+      </c>
+      <c r="O215" t="n">
+        <v>3</v>
+      </c>
+      <c r="P215" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>12</v>
+      </c>
+      <c r="R215" t="n">
+        <v>10</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="U215" t="n">
+        <v>167</v>
+      </c>
+      <c r="V215" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0</v>
+      </c>
+      <c r="X215" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr"/>
+      <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr"/>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr"/>
+      <c r="AQ215" t="inlineStr"/>
+      <c r="AR215" t="inlineStr"/>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AU215" t="inlineStr"/>
+      <c r="AV215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr"/>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr"/>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
+      <c r="BI215" t="inlineStr"/>
+      <c r="BJ215" t="inlineStr"/>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="inlineStr"/>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
+      <c r="BO215" t="inlineStr"/>
+      <c r="BP215" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39989,6 +39989,4250 @@
       <c r="BO215" t="inlineStr"/>
       <c r="BP215" t="inlineStr"/>
     </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>lMloGBdO</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>45493</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wild horse pass stadium
+  chandler  az </t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>57</v>
+      </c>
+      <c r="L216" t="n">
+        <v>43</v>
+      </c>
+      <c r="M216" t="n">
+        <v>14</v>
+      </c>
+      <c r="N216" t="n">
+        <v>8</v>
+      </c>
+      <c r="O216" t="n">
+        <v>6</v>
+      </c>
+      <c r="P216" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>8</v>
+      </c>
+      <c r="R216" t="n">
+        <v>7</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="U216" t="n">
+        <v>167</v>
+      </c>
+      <c r="V216" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0</v>
+      </c>
+      <c r="X216" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
+      <c r="AJ216" t="inlineStr"/>
+      <c r="AK216" t="inlineStr"/>
+      <c r="AL216" t="inlineStr"/>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr"/>
+      <c r="AO216" t="inlineStr"/>
+      <c r="AP216" t="inlineStr"/>
+      <c r="AQ216" t="inlineStr"/>
+      <c r="AR216" t="inlineStr"/>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AU216" t="inlineStr"/>
+      <c r="AV216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr"/>
+      <c r="AX216" t="inlineStr"/>
+      <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr"/>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr"/>
+      <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr"/>
+      <c r="BI216" t="inlineStr"/>
+      <c r="BJ216" t="inlineStr"/>
+      <c r="BK216" t="inlineStr"/>
+      <c r="BL216" t="inlineStr"/>
+      <c r="BM216" t="inlineStr"/>
+      <c r="BN216" t="inlineStr"/>
+      <c r="BO216" t="inlineStr"/>
+      <c r="BP216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>fNexIXRB</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>45492.875</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hassan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lynn family stadium
+  louisville  ky </t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>15304</v>
+      </c>
+      <c r="F217" t="n">
+        <v>10418</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>43</v>
+      </c>
+      <c r="L217" t="n">
+        <v>57</v>
+      </c>
+      <c r="M217" t="n">
+        <v>20</v>
+      </c>
+      <c r="N217" t="n">
+        <v>10</v>
+      </c>
+      <c r="O217" t="n">
+        <v>4</v>
+      </c>
+      <c r="P217" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>16</v>
+      </c>
+      <c r="R217" t="n">
+        <v>17</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="U217" t="n">
+        <v>167</v>
+      </c>
+      <c r="V217" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0</v>
+      </c>
+      <c r="X217" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
+      <c r="AJ217" t="inlineStr"/>
+      <c r="AK217" t="inlineStr"/>
+      <c r="AL217" t="inlineStr"/>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr"/>
+      <c r="AO217" t="inlineStr"/>
+      <c r="AP217" t="inlineStr"/>
+      <c r="AQ217" t="inlineStr"/>
+      <c r="AR217" t="inlineStr"/>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AU217" t="inlineStr"/>
+      <c r="AV217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr"/>
+      <c r="AX217" t="inlineStr"/>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr"/>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr"/>
+      <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr"/>
+      <c r="BI217" t="inlineStr"/>
+      <c r="BJ217" t="inlineStr"/>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="inlineStr"/>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
+      <c r="BO217" t="inlineStr"/>
+      <c r="BP217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>00dYIDC5</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>45492.85416666666</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2883</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>59</v>
+      </c>
+      <c r="L218" t="n">
+        <v>41</v>
+      </c>
+      <c r="M218" t="n">
+        <v>25</v>
+      </c>
+      <c r="N218" t="n">
+        <v>7</v>
+      </c>
+      <c r="O218" t="n">
+        <v>9</v>
+      </c>
+      <c r="P218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>16</v>
+      </c>
+      <c r="R218" t="n">
+        <v>15</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="U218" t="n">
+        <v>167</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W218" t="n">
+        <v>0</v>
+      </c>
+      <c r="X218" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
+      <c r="AJ218" t="inlineStr"/>
+      <c r="AK218" t="inlineStr"/>
+      <c r="AL218" t="inlineStr"/>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr"/>
+      <c r="AO218" t="inlineStr"/>
+      <c r="AP218" t="inlineStr"/>
+      <c r="AQ218" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>62</v>
+      </c>
+      <c r="AW218" t="inlineStr"/>
+      <c r="AX218" t="inlineStr"/>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr"/>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr"/>
+      <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
+      <c r="BI218" t="inlineStr"/>
+      <c r="BJ218" t="inlineStr"/>
+      <c r="BK218" t="inlineStr"/>
+      <c r="BL218" t="inlineStr"/>
+      <c r="BM218" t="inlineStr"/>
+      <c r="BN218" t="inlineStr"/>
+      <c r="BO218" t="inlineStr"/>
+      <c r="BP218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>6catHisI</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>45492.85416666666</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheer j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wakemed soccer park
+  cary  nc </t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2054</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>30</v>
+      </c>
+      <c r="L219" t="n">
+        <v>70</v>
+      </c>
+      <c r="M219" t="n">
+        <v>7</v>
+      </c>
+      <c r="N219" t="n">
+        <v>13</v>
+      </c>
+      <c r="O219" t="n">
+        <v>2</v>
+      </c>
+      <c r="P219" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>14</v>
+      </c>
+      <c r="R219" t="n">
+        <v>10</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="U219" t="n">
+        <v>167</v>
+      </c>
+      <c r="V219" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W219" t="n">
+        <v>0</v>
+      </c>
+      <c r="X219" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="inlineStr"/>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr"/>
+      <c r="AJ219" t="inlineStr"/>
+      <c r="AK219" t="inlineStr"/>
+      <c r="AL219" t="inlineStr"/>
+      <c r="AM219" t="inlineStr"/>
+      <c r="AN219" t="inlineStr"/>
+      <c r="AO219" t="inlineStr"/>
+      <c r="AP219" t="inlineStr"/>
+      <c r="AQ219" t="inlineStr"/>
+      <c r="AR219" t="inlineStr"/>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AU219" t="inlineStr"/>
+      <c r="AV219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr"/>
+      <c r="AX219" t="inlineStr"/>
+      <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr"/>
+      <c r="BA219" t="inlineStr"/>
+      <c r="BB219" t="inlineStr"/>
+      <c r="BC219" t="inlineStr"/>
+      <c r="BD219" t="inlineStr"/>
+      <c r="BE219" t="inlineStr"/>
+      <c r="BF219" t="inlineStr"/>
+      <c r="BG219" t="inlineStr"/>
+      <c r="BH219" t="inlineStr"/>
+      <c r="BI219" t="inlineStr"/>
+      <c r="BJ219" t="inlineStr"/>
+      <c r="BK219" t="inlineStr"/>
+      <c r="BL219" t="inlineStr"/>
+      <c r="BM219" t="inlineStr"/>
+      <c r="BN219" t="inlineStr"/>
+      <c r="BO219" t="inlineStr"/>
+      <c r="BP219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>E3M7XCRb</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>45493.95833333334</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wiseman t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4258</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>42</v>
+      </c>
+      <c r="L220" t="n">
+        <v>58</v>
+      </c>
+      <c r="M220" t="n">
+        <v>13</v>
+      </c>
+      <c r="N220" t="n">
+        <v>15</v>
+      </c>
+      <c r="O220" t="n">
+        <v>6</v>
+      </c>
+      <c r="P220" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>10</v>
+      </c>
+      <c r="R220" t="n">
+        <v>18</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="U220" t="n">
+        <v>167</v>
+      </c>
+      <c r="V220" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0</v>
+      </c>
+      <c r="X220" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
+      <c r="AE220" t="inlineStr"/>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr"/>
+      <c r="AI220" t="inlineStr"/>
+      <c r="AJ220" t="inlineStr"/>
+      <c r="AK220" t="inlineStr"/>
+      <c r="AL220" t="inlineStr"/>
+      <c r="AM220" t="inlineStr"/>
+      <c r="AN220" t="inlineStr"/>
+      <c r="AO220" t="inlineStr"/>
+      <c r="AP220" t="inlineStr"/>
+      <c r="AQ220" t="inlineStr"/>
+      <c r="AR220" t="inlineStr"/>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AU220" t="inlineStr"/>
+      <c r="AV220" t="inlineStr"/>
+      <c r="AW220" t="n">
+        <v>21.57142857142857</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>182.7142857142857</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>56</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>273571.4285714286</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="BC220" t="inlineStr"/>
+      <c r="BD220" t="inlineStr"/>
+      <c r="BE220" t="inlineStr"/>
+      <c r="BF220" t="inlineStr"/>
+      <c r="BG220" t="inlineStr"/>
+      <c r="BH220" t="inlineStr"/>
+      <c r="BI220" t="inlineStr"/>
+      <c r="BJ220" t="inlineStr"/>
+      <c r="BK220" t="inlineStr"/>
+      <c r="BL220" t="inlineStr"/>
+      <c r="BM220" t="inlineStr"/>
+      <c r="BN220" t="inlineStr"/>
+      <c r="BO220" t="inlineStr"/>
+      <c r="BP220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>IyTbZYdn</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>45493.91666666666</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arroyo l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F221" t="n">
+        <v>9096</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>64</v>
+      </c>
+      <c r="L221" t="n">
+        <v>36</v>
+      </c>
+      <c r="M221" t="n">
+        <v>6</v>
+      </c>
+      <c r="N221" t="n">
+        <v>13</v>
+      </c>
+      <c r="O221" t="n">
+        <v>4</v>
+      </c>
+      <c r="P221" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>10</v>
+      </c>
+      <c r="R221" t="n">
+        <v>8</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="U221" t="n">
+        <v>167</v>
+      </c>
+      <c r="V221" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W221" t="n">
+        <v>0</v>
+      </c>
+      <c r="X221" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA221" t="inlineStr"/>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+      <c r="AE221" t="inlineStr"/>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
+      <c r="AI221" t="inlineStr"/>
+      <c r="AJ221" t="inlineStr"/>
+      <c r="AK221" t="inlineStr"/>
+      <c r="AL221" t="inlineStr"/>
+      <c r="AM221" t="inlineStr"/>
+      <c r="AN221" t="inlineStr"/>
+      <c r="AO221" t="inlineStr"/>
+      <c r="AP221" t="inlineStr"/>
+      <c r="AQ221" t="inlineStr"/>
+      <c r="AR221" t="inlineStr"/>
+      <c r="AS221" t="inlineStr"/>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AU221" t="inlineStr"/>
+      <c r="AV221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr"/>
+      <c r="AX221" t="inlineStr"/>
+      <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr"/>
+      <c r="BA221" t="inlineStr"/>
+      <c r="BB221" t="inlineStr"/>
+      <c r="BC221" t="inlineStr"/>
+      <c r="BD221" t="inlineStr"/>
+      <c r="BE221" t="inlineStr"/>
+      <c r="BF221" t="inlineStr"/>
+      <c r="BG221" t="inlineStr"/>
+      <c r="BH221" t="inlineStr"/>
+      <c r="BI221" t="inlineStr"/>
+      <c r="BJ221" t="inlineStr"/>
+      <c r="BK221" t="inlineStr"/>
+      <c r="BL221" t="inlineStr"/>
+      <c r="BM221" t="inlineStr"/>
+      <c r="BN221" t="inlineStr"/>
+      <c r="BO221" t="inlineStr"/>
+      <c r="BP221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>SCmkFVBU</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nichols a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F222" t="n">
+        <v>3950</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>44</v>
+      </c>
+      <c r="L222" t="n">
+        <v>56</v>
+      </c>
+      <c r="M222" t="n">
+        <v>9</v>
+      </c>
+      <c r="N222" t="n">
+        <v>7</v>
+      </c>
+      <c r="O222" t="n">
+        <v>5</v>
+      </c>
+      <c r="P222" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>19</v>
+      </c>
+      <c r="R222" t="n">
+        <v>26</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="U222" t="n">
+        <v>167</v>
+      </c>
+      <c r="V222" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W222" t="n">
+        <v>0</v>
+      </c>
+      <c r="X222" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+      <c r="AE222" t="inlineStr"/>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr"/>
+      <c r="AI222" t="inlineStr"/>
+      <c r="AJ222" t="inlineStr"/>
+      <c r="AK222" t="inlineStr"/>
+      <c r="AL222" t="inlineStr"/>
+      <c r="AM222" t="inlineStr"/>
+      <c r="AN222" t="inlineStr"/>
+      <c r="AO222" t="inlineStr"/>
+      <c r="AP222" t="inlineStr"/>
+      <c r="AQ222" t="inlineStr"/>
+      <c r="AR222" t="inlineStr"/>
+      <c r="AS222" t="inlineStr"/>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AU222" t="inlineStr"/>
+      <c r="AV222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr"/>
+      <c r="AX222" t="inlineStr"/>
+      <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr"/>
+      <c r="BA222" t="inlineStr"/>
+      <c r="BB222" t="inlineStr"/>
+      <c r="BC222" t="inlineStr"/>
+      <c r="BD222" t="inlineStr"/>
+      <c r="BE222" t="inlineStr"/>
+      <c r="BF222" t="inlineStr"/>
+      <c r="BG222" t="inlineStr"/>
+      <c r="BH222" t="inlineStr"/>
+      <c r="BI222" t="inlineStr"/>
+      <c r="BJ222" t="inlineStr"/>
+      <c r="BK222" t="inlineStr"/>
+      <c r="BL222" t="inlineStr"/>
+      <c r="BM222" t="inlineStr"/>
+      <c r="BN222" t="inlineStr"/>
+      <c r="BO222" t="inlineStr"/>
+      <c r="BP222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>8QLBWWt5</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>45493.875</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F223" t="n">
+        <v>5602</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>34</v>
+      </c>
+      <c r="L223" t="n">
+        <v>66</v>
+      </c>
+      <c r="M223" t="n">
+        <v>15</v>
+      </c>
+      <c r="N223" t="n">
+        <v>5</v>
+      </c>
+      <c r="O223" t="n">
+        <v>7</v>
+      </c>
+      <c r="P223" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>12</v>
+      </c>
+      <c r="R223" t="n">
+        <v>19</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="U223" t="n">
+        <v>167</v>
+      </c>
+      <c r="V223" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W223" t="n">
+        <v>0</v>
+      </c>
+      <c r="X223" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA223" t="inlineStr"/>
+      <c r="AB223" t="inlineStr"/>
+      <c r="AC223" t="inlineStr"/>
+      <c r="AD223" t="inlineStr"/>
+      <c r="AE223" t="inlineStr"/>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr"/>
+      <c r="AI223" t="inlineStr"/>
+      <c r="AJ223" t="inlineStr"/>
+      <c r="AK223" t="inlineStr"/>
+      <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr"/>
+      <c r="AO223" t="inlineStr"/>
+      <c r="AP223" t="inlineStr"/>
+      <c r="AQ223" t="inlineStr"/>
+      <c r="AR223" t="inlineStr"/>
+      <c r="AS223" t="inlineStr"/>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AU223" t="inlineStr"/>
+      <c r="AV223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr"/>
+      <c r="AX223" t="inlineStr"/>
+      <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr"/>
+      <c r="BA223" t="inlineStr"/>
+      <c r="BB223" t="inlineStr"/>
+      <c r="BC223" t="inlineStr"/>
+      <c r="BD223" t="inlineStr"/>
+      <c r="BE223" t="inlineStr"/>
+      <c r="BF223" t="inlineStr"/>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
+      <c r="BI223" t="inlineStr"/>
+      <c r="BJ223" t="inlineStr"/>
+      <c r="BK223" t="inlineStr"/>
+      <c r="BL223" t="inlineStr"/>
+      <c r="BM223" t="inlineStr"/>
+      <c r="BN223" t="inlineStr"/>
+      <c r="BO223" t="inlineStr"/>
+      <c r="BP223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>voUfzFst</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>45493.83333333334</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michael a  carroll stadium
+  indianapolis  in </t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>12111</v>
+      </c>
+      <c r="F224" t="n">
+        <v>10636</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>2</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>51</v>
+      </c>
+      <c r="L224" t="n">
+        <v>49</v>
+      </c>
+      <c r="M224" t="n">
+        <v>8</v>
+      </c>
+      <c r="N224" t="n">
+        <v>20</v>
+      </c>
+      <c r="O224" t="n">
+        <v>2</v>
+      </c>
+      <c r="P224" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>13</v>
+      </c>
+      <c r="R224" t="n">
+        <v>15</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="U224" t="n">
+        <v>167</v>
+      </c>
+      <c r="V224" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W224" t="n">
+        <v>0</v>
+      </c>
+      <c r="X224" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA224" t="inlineStr"/>
+      <c r="AB224" t="inlineStr"/>
+      <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
+      <c r="AE224" t="inlineStr"/>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr"/>
+      <c r="AJ224" t="inlineStr"/>
+      <c r="AK224" t="inlineStr"/>
+      <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr"/>
+      <c r="AO224" t="inlineStr"/>
+      <c r="AP224" t="inlineStr"/>
+      <c r="AQ224" t="inlineStr"/>
+      <c r="AR224" t="inlineStr"/>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AU224" t="inlineStr"/>
+      <c r="AV224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr"/>
+      <c r="AX224" t="inlineStr"/>
+      <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr"/>
+      <c r="BA224" t="inlineStr"/>
+      <c r="BB224" t="inlineStr"/>
+      <c r="BC224" t="inlineStr"/>
+      <c r="BD224" t="inlineStr"/>
+      <c r="BE224" t="inlineStr"/>
+      <c r="BF224" t="inlineStr"/>
+      <c r="BG224" t="inlineStr"/>
+      <c r="BH224" t="inlineStr"/>
+      <c r="BI224" t="inlineStr"/>
+      <c r="BJ224" t="inlineStr"/>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="inlineStr"/>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
+      <c r="BO224" t="inlineStr"/>
+      <c r="BP224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>p0lFJwSk</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>45493.98958333334</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F225" t="n">
+        <v>23568</v>
+      </c>
+      <c r="G225" t="n">
+        <v>3</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>50</v>
+      </c>
+      <c r="L225" t="n">
+        <v>50</v>
+      </c>
+      <c r="M225" t="n">
+        <v>10</v>
+      </c>
+      <c r="N225" t="n">
+        <v>9</v>
+      </c>
+      <c r="O225" t="n">
+        <v>7</v>
+      </c>
+      <c r="P225" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>9</v>
+      </c>
+      <c r="R225" t="n">
+        <v>13</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="U225" t="n">
+        <v>167</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W225" t="n">
+        <v>0</v>
+      </c>
+      <c r="X225" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="inlineStr"/>
+      <c r="AA225" t="inlineStr"/>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AE225" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>3825000</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>177.5454545454545</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>2902272.727272727</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>181</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>64</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>1470312.5</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>70.4375</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>26.08695652173913</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>181.9565217391304</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>67.21739130434783</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>1379565.217391304</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>69.65217391304348</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>73</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>775000</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>vNmJIcsd</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F226" t="n">
+        <v>32905</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>3</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>67</v>
+      </c>
+      <c r="L226" t="n">
+        <v>33</v>
+      </c>
+      <c r="M226" t="n">
+        <v>22</v>
+      </c>
+      <c r="N226" t="n">
+        <v>7</v>
+      </c>
+      <c r="O226" t="n">
+        <v>5</v>
+      </c>
+      <c r="P226" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>11</v>
+      </c>
+      <c r="R226" t="n">
+        <v>14</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="U226" t="n">
+        <v>167</v>
+      </c>
+      <c r="V226" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W226" t="n">
+        <v>0</v>
+      </c>
+      <c r="X226" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y226" t="inlineStr"/>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr"/>
+      <c r="AE226" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>3275000</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>4040000</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>26.05882352941176</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>176.0588235294118</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>66.35294117647059</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>2305000</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>69.64705882352941</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>179.3636363636364</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>66.22727272727273</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>1243181.818181818</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>72.59090909090909</v>
+      </c>
+      <c r="BC226" t="inlineStr"/>
+      <c r="BD226" t="inlineStr"/>
+      <c r="BE226" t="inlineStr"/>
+      <c r="BF226" t="inlineStr"/>
+      <c r="BG226" t="inlineStr"/>
+      <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>189</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>58</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>MHXbihN8</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F227" t="n">
+        <v>24114</v>
+      </c>
+      <c r="G227" t="n">
+        <v>3</v>
+      </c>
+      <c r="H227" t="n">
+        <v>4</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>43</v>
+      </c>
+      <c r="L227" t="n">
+        <v>57</v>
+      </c>
+      <c r="M227" t="n">
+        <v>3</v>
+      </c>
+      <c r="N227" t="n">
+        <v>4</v>
+      </c>
+      <c r="O227" t="n">
+        <v>3</v>
+      </c>
+      <c r="P227" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>8</v>
+      </c>
+      <c r="R227" t="n">
+        <v>18</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="U227" t="n">
+        <v>167</v>
+      </c>
+      <c r="V227" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W227" t="n">
+        <v>0</v>
+      </c>
+      <c r="X227" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y227" t="inlineStr"/>
+      <c r="Z227" t="inlineStr"/>
+      <c r="AA227" t="inlineStr"/>
+      <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AE227" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>2717500</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>2095500</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>176.875</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>66.29166666666667</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>1518750</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>1213750</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>70</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>175</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>62</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>875000</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>69kBKJCq</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>45493.9375</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="n">
+        <v>3</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>38</v>
+      </c>
+      <c r="L228" t="n">
+        <v>62</v>
+      </c>
+      <c r="M228" t="n">
+        <v>10</v>
+      </c>
+      <c r="N228" t="n">
+        <v>12</v>
+      </c>
+      <c r="O228" t="n">
+        <v>4</v>
+      </c>
+      <c r="P228" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>10</v>
+      </c>
+      <c r="R228" t="n">
+        <v>10</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="U228" t="n">
+        <v>167</v>
+      </c>
+      <c r="V228" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W228" t="n">
+        <v>0</v>
+      </c>
+      <c r="X228" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y228" t="inlineStr"/>
+      <c r="Z228" t="inlineStr"/>
+      <c r="AA228" t="inlineStr"/>
+      <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AE228" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>179.2222222222222</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1364444.444444444</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>178.7272727272727</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>65.63636363636364</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>1502727.272727273</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>503500</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>178.6428571428571</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>1661428.571428571</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>70.42857142857143</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>183</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>77</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>204</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>h29zRLZF</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>20738</v>
+      </c>
+      <c r="F229" t="n">
+        <v>20738</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>56</v>
+      </c>
+      <c r="L229" t="n">
+        <v>44</v>
+      </c>
+      <c r="M229" t="n">
+        <v>11</v>
+      </c>
+      <c r="N229" t="n">
+        <v>11</v>
+      </c>
+      <c r="O229" t="n">
+        <v>4</v>
+      </c>
+      <c r="P229" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>11</v>
+      </c>
+      <c r="R229" t="n">
+        <v>11</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="U229" t="n">
+        <v>167</v>
+      </c>
+      <c r="V229" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W229" t="n">
+        <v>0</v>
+      </c>
+      <c r="X229" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE229" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>825000</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>67.18181818181819</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>1602272.727272727</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>180</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>64.82352941176471</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>942352.9411764706</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>66.82352941176471</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>25.92857142857143</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>182.4285714285714</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>65.78571428571429</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>1938571.428571429</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>70.35714285714286</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>179</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>34</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>QF7rPa4S</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F230" t="n">
+        <v>19679</v>
+      </c>
+      <c r="G230" t="n">
+        <v>2</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>49</v>
+      </c>
+      <c r="L230" t="n">
+        <v>51</v>
+      </c>
+      <c r="M230" t="n">
+        <v>7</v>
+      </c>
+      <c r="N230" t="n">
+        <v>3</v>
+      </c>
+      <c r="O230" t="n">
+        <v>3</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>19</v>
+      </c>
+      <c r="R230" t="n">
+        <v>9</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="U230" t="n">
+        <v>167</v>
+      </c>
+      <c r="V230" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W230" t="n">
+        <v>0</v>
+      </c>
+      <c r="X230" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
+      <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr"/>
+      <c r="AE230" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>63.18181818181818</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1103636.363636364</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>2652000</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>27.53846153846154</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>177.0769230769231</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>67.38461538461539</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>1767307.692307692</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>70.53846153846153</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>180</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>65.36363636363636</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>1289772.727272727</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>32.66666666666666</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>184</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>199</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>199</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>125</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>nP8vQukM</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F231" t="n">
+        <v>19876</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>61</v>
+      </c>
+      <c r="L231" t="n">
+        <v>39</v>
+      </c>
+      <c r="M231" t="n">
+        <v>9</v>
+      </c>
+      <c r="N231" t="n">
+        <v>4</v>
+      </c>
+      <c r="O231" t="n">
+        <v>5</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>15</v>
+      </c>
+      <c r="R231" t="n">
+        <v>18</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="U231" t="n">
+        <v>167</v>
+      </c>
+      <c r="V231" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y231" t="inlineStr"/>
+      <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE231" t="n">
+        <v>28.27272727272727</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>181.5454545454545</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>1321818.181818182</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1842500</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>25.46666666666667</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>66.93333333333334</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>23.13333333333333</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>59.66666666666666</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>580000</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>68</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>129</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>137</v>
+      </c>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="inlineStr"/>
+      <c r="BM231" t="inlineStr"/>
+      <c r="BN231" t="inlineStr"/>
+      <c r="BO231" t="inlineStr"/>
+      <c r="BP231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>AszX60rp</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F232" t="n">
+        <v>42601</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>33</v>
+      </c>
+      <c r="L232" t="n">
+        <v>67</v>
+      </c>
+      <c r="M232" t="n">
+        <v>13</v>
+      </c>
+      <c r="N232" t="n">
+        <v>13</v>
+      </c>
+      <c r="O232" t="n">
+        <v>6</v>
+      </c>
+      <c r="P232" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>10</v>
+      </c>
+      <c r="R232" t="n">
+        <v>9</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="U232" t="n">
+        <v>167</v>
+      </c>
+      <c r="V232" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W232" t="n">
+        <v>0</v>
+      </c>
+      <c r="X232" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y232" t="inlineStr"/>
+      <c r="Z232" t="inlineStr"/>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AE232" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>179</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1174090.909090909</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>68.90909090909091</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>182</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>3570000</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>26.46666666666667</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>179.0666666666667</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>1273333.333333333</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>70.06666666666666</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>65.5625</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>1309375</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>71.8125</v>
+      </c>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="n">
+        <v>37</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>63</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>jix3jCxF</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F233" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>57</v>
+      </c>
+      <c r="L233" t="n">
+        <v>43</v>
+      </c>
+      <c r="M233" t="n">
+        <v>3</v>
+      </c>
+      <c r="N233" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>13</v>
+      </c>
+      <c r="R233" t="n">
+        <v>17</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="U233" t="n">
+        <v>167</v>
+      </c>
+      <c r="V233" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W233" t="n">
+        <v>0</v>
+      </c>
+      <c r="X233" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y233" t="inlineStr"/>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AE233" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>179.1818181818182</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>1318181.818181818</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>3235909.090909091</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>175.875</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>65.91666666666667</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>1666250</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>72.58333333333333</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>181.3809523809524</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>1938333.333333333</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>69.80952380952381</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>124</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>127</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>117</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>990000</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>h6Py6Kcj</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F234" t="n">
+        <v>20318</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2</v>
+      </c>
+      <c r="H234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>45</v>
+      </c>
+      <c r="L234" t="n">
+        <v>55</v>
+      </c>
+      <c r="M234" t="n">
+        <v>12</v>
+      </c>
+      <c r="N234" t="n">
+        <v>9</v>
+      </c>
+      <c r="O234" t="n">
+        <v>6</v>
+      </c>
+      <c r="P234" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>9</v>
+      </c>
+      <c r="R234" t="n">
+        <v>9</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
+        <v>167</v>
+      </c>
+      <c r="V234" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W234" t="n">
+        <v>0</v>
+      </c>
+      <c r="X234" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y234" t="inlineStr"/>
+      <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AE234" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>73.81818181818181</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>6020454.545454546</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>77.18181818181819</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>68.36363636363636</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>2327272.727272727</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>183.3529411764706</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>65.05882352941177</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>1895588.235294118</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>74.70588235294117</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>180.7083333333333</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>62.54166666666666</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>824375</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>67.54166666666667</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>372</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>57825000</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>384</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>337</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>8875000</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>WdOu5vDd</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F235" t="n">
+        <v>28260</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>55</v>
+      </c>
+      <c r="L235" t="n">
+        <v>45</v>
+      </c>
+      <c r="M235" t="n">
+        <v>9</v>
+      </c>
+      <c r="N235" t="n">
+        <v>6</v>
+      </c>
+      <c r="O235" t="n">
+        <v>1</v>
+      </c>
+      <c r="P235" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>17</v>
+      </c>
+      <c r="R235" t="n">
+        <v>17</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="U235" t="n">
+        <v>167</v>
+      </c>
+      <c r="V235" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W235" t="n">
+        <v>0</v>
+      </c>
+      <c r="X235" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr"/>
+      <c r="AA235" t="inlineStr"/>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr"/>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE235" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>1222222.222222222</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>1017500</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>178.8235294117647</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>64.82352941176471</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>748529.4117647059</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>69.76470588235294</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>23.47058823529412</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>59.05882352941177</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>437352.9411764706</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>66.94117647058823</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>177.7142857142857</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>493</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>34100000</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>530</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>561</v>
+      </c>
+      <c r="BO235" t="n">
+        <v>42350000</v>
+      </c>
+      <c r="BP235" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>KCHNTNkc</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F236" t="n">
+        <v>19828</v>
+      </c>
+      <c r="G236" t="n">
+        <v>3</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>39</v>
+      </c>
+      <c r="L236" t="n">
+        <v>61</v>
+      </c>
+      <c r="M236" t="n">
+        <v>12</v>
+      </c>
+      <c r="N236" t="n">
+        <v>6</v>
+      </c>
+      <c r="O236" t="n">
+        <v>6</v>
+      </c>
+      <c r="P236" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>19</v>
+      </c>
+      <c r="R236" t="n">
+        <v>15</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>CKCtVmJf</t>
+        </is>
+      </c>
+      <c r="U236" t="n">
+        <v>167</v>
+      </c>
+      <c r="V236" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W236" t="n">
+        <v>0</v>
+      </c>
+      <c r="X236" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="inlineStr"/>
+      <c r="AB236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AE236" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>1732000</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>1640454.545454545</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>180.3125</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>64</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>1655625</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>25.04166666666667</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>177.2083333333333</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>4251875</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>70.41666666666667</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>319</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>17800000</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>361</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN236" t="n">
+        <v>199</v>
+      </c>
+      <c r="BO236" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="BP236" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>b3GRSs53</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F237" t="n">
+        <v>22827</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>58</v>
+      </c>
+      <c r="L237" t="n">
+        <v>42</v>
+      </c>
+      <c r="M237" t="n">
+        <v>9</v>
+      </c>
+      <c r="N237" t="n">
+        <v>6</v>
+      </c>
+      <c r="O237" t="n">
+        <v>4</v>
+      </c>
+      <c r="P237" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>11</v>
+      </c>
+      <c r="R237" t="n">
+        <v>20</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="U237" t="n">
+        <v>167</v>
+      </c>
+      <c r="V237" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W237" t="n">
+        <v>0</v>
+      </c>
+      <c r="X237" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr"/>
+      <c r="AE237" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>2192500</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>72</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>22.55555555555556</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>65.88888888888889</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>1555555.555555556</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>25.69565217391304</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>180.8260869565217</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>1.217391304347826</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>66.60869565217391</v>
+      </c>
+      <c r="AU237" t="n">
+        <v>3477391.304347826</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>21.68421052631579</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>63.52631578947368</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>1939473.684210526</v>
+      </c>
+      <c r="BB237" t="n">
+        <v>72.57894736842105</v>
+      </c>
+      <c r="BC237" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>185</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>475000</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>118</v>
+      </c>
+      <c r="BO237" t="n">
+        <v>1620000</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>tS5WR1K9</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F238" t="n">
+        <v>18962</v>
+      </c>
+      <c r="G238" t="n">
+        <v>3</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>45</v>
+      </c>
+      <c r="L238" t="n">
+        <v>55</v>
+      </c>
+      <c r="M238" t="n">
+        <v>13</v>
+      </c>
+      <c r="N238" t="n">
+        <v>10</v>
+      </c>
+      <c r="O238" t="n">
+        <v>6</v>
+      </c>
+      <c r="P238" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>13</v>
+      </c>
+      <c r="R238" t="n">
+        <v>10</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="U238" t="n">
+        <v>167</v>
+      </c>
+      <c r="V238" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W238" t="n">
+        <v>0</v>
+      </c>
+      <c r="X238" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y238" t="inlineStr"/>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="inlineStr"/>
+      <c r="AB238" t="inlineStr"/>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AE238" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>3277272.727272727</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>73.72727272727273</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>182.9090909090909</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>65.72727272727273</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>2627727.272727273</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>26.23809523809524</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>185.7142857142857</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>65.71428571428571</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>1302857.142857143</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>69.71428571428571</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>29.10526315789474</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>182.421052631579</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>66.10526315789474</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>780263.1578947369</v>
+      </c>
+      <c r="BB238" t="n">
+        <v>66.94736842105263</v>
+      </c>
+      <c r="BC238" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>175</v>
+      </c>
+      <c r="BE238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>275000</v>
+      </c>
+      <c r="BI238" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ238" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BK238" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>185</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
